--- a/Tableurs Tenrac Final.xlsx
+++ b/Tableurs Tenrac Final.xlsx
@@ -1,38 +1,46 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29711"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
   <workbookPr defaultThemeVersion="166925"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{BF795BEA-CE48-4AAD-854D-9909685C4E29}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y25010156\Downloads\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B5BB3E-3431-4B40-B745-D9F7E12F9930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="12" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Tenrac" sheetId="9" r:id="rId1"/>
-    <sheet name="Carte_membre" sheetId="12" r:id="rId2"/>
-    <sheet name="Organisme" sheetId="1" r:id="rId3"/>
-    <sheet name="Club" sheetId="2" r:id="rId4"/>
-    <sheet name="Ordre" sheetId="27" r:id="rId5"/>
-    <sheet name="Grade" sheetId="5" r:id="rId6"/>
-    <sheet name="Rang" sheetId="6" r:id="rId7"/>
-    <sheet name="Titre" sheetId="7" r:id="rId8"/>
-    <sheet name="Dignité" sheetId="8" r:id="rId9"/>
-    <sheet name="Réunion" sheetId="10" r:id="rId10"/>
-    <sheet name="Repas" sheetId="19" r:id="rId11"/>
-    <sheet name="Ingrédient" sheetId="11" r:id="rId12"/>
-    <sheet name="Légume" sheetId="20" r:id="rId13"/>
-    <sheet name="Plat" sheetId="13" r:id="rId14"/>
-    <sheet name="PlatContientIng" sheetId="14" r:id="rId15"/>
-    <sheet name="machine" sheetId="17" r:id="rId16"/>
-    <sheet name="Plat avec Machine" sheetId="21" r:id="rId17"/>
-    <sheet name="EntrerienMachine" sheetId="18" r:id="rId18"/>
-    <sheet name="Contrainte et ingrédient" sheetId="26" r:id="rId19"/>
-    <sheet name="Contrainte" sheetId="22" r:id="rId20"/>
-    <sheet name="Conviction" sheetId="25" r:id="rId21"/>
-    <sheet name="Allergene" sheetId="23" r:id="rId22"/>
-    <sheet name="Croyance" sheetId="24" r:id="rId23"/>
-    <sheet name="Sauce" sheetId="15" r:id="rId24"/>
-    <sheet name="SauceAccompagne" sheetId="16" r:id="rId25"/>
+    <sheet name="PARTICIPE" sheetId="28" r:id="rId2"/>
+    <sheet name="EST_COMPOSE_DE" sheetId="29" r:id="rId3"/>
+    <sheet name="EST_SUJET_A" sheetId="30" r:id="rId4"/>
+    <sheet name="Carte_membre" sheetId="12" r:id="rId5"/>
+    <sheet name="Organisme" sheetId="1" r:id="rId6"/>
+    <sheet name="Club" sheetId="2" r:id="rId7"/>
+    <sheet name="Ordre" sheetId="27" r:id="rId8"/>
+    <sheet name="Grade" sheetId="5" r:id="rId9"/>
+    <sheet name="Rang" sheetId="6" r:id="rId10"/>
+    <sheet name="Titre" sheetId="7" r:id="rId11"/>
+    <sheet name="Dignité" sheetId="8" r:id="rId12"/>
+    <sheet name="Réunion" sheetId="10" r:id="rId13"/>
+    <sheet name="Repas" sheetId="19" r:id="rId14"/>
+    <sheet name="Ingrédient" sheetId="11" r:id="rId15"/>
+    <sheet name="Légume" sheetId="20" r:id="rId16"/>
+    <sheet name="Plat" sheetId="13" r:id="rId17"/>
+    <sheet name="CONTIENT" sheetId="14" r:id="rId18"/>
+    <sheet name="machine" sheetId="17" r:id="rId19"/>
+    <sheet name="UTILISE" sheetId="21" r:id="rId20"/>
+    <sheet name="Entrerien" sheetId="18" r:id="rId21"/>
+    <sheet name="POSSEDE " sheetId="26" r:id="rId22"/>
+    <sheet name="Contrainte" sheetId="22" r:id="rId23"/>
+    <sheet name="Conviction" sheetId="25" r:id="rId24"/>
+    <sheet name="Allergene" sheetId="23" r:id="rId25"/>
+    <sheet name="Croyance" sheetId="24" r:id="rId26"/>
+    <sheet name="Sauce" sheetId="15" r:id="rId27"/>
+    <sheet name="ACCOMPAGNE" sheetId="16" r:id="rId28"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -46,16 +54,17 @@
         <xcalcf:feature name="microsoft.com:FV"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="605" uniqueCount="455">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="458">
   <si>
     <t>idTenrac</t>
   </si>
@@ -702,18 +711,9 @@
     <t>12 rue de la Durance, 05130 Tallard</t>
   </si>
   <si>
-    <t>idCarte</t>
-  </si>
-  <si>
     <t>codePersonnel</t>
   </si>
   <si>
-    <t>nomTenrac</t>
-  </si>
-  <si>
-    <t>raisonSociale</t>
-  </si>
-  <si>
     <t>numSIRET</t>
   </si>
   <si>
@@ -891,9 +891,6 @@
     <t>MAN-9-10</t>
   </si>
   <si>
-    <t>MartinNévot</t>
-  </si>
-  <si>
     <t>IUT Aix  (Gaston Berger)</t>
   </si>
   <si>
@@ -1065,9 +1062,6 @@
     <t>Centre-bourg, 73000 Saint-Gervais</t>
   </si>
   <si>
-    <t>nomRepas</t>
-  </si>
-  <si>
     <t>idP</t>
   </si>
   <si>
@@ -1095,25 +1089,6 @@
     <t>Repas Symbolique Suprême</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Calibri"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>R</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-      </rPr>
-      <t>ite du Tender Suprême</t>
-    </r>
-  </si>
-  <si>
     <t>Festin Raclette Royale</t>
   </si>
   <si>
@@ -1189,15 +1164,9 @@
     <t>Viande à kebab</t>
   </si>
   <si>
-    <t>idL</t>
-  </si>
-  <si>
     <t>IdIng</t>
   </si>
   <si>
-    <t>nomLégume</t>
-  </si>
-  <si>
     <t>nomPlat</t>
   </si>
   <si>
@@ -1312,24 +1281,9 @@
     <t>libelle</t>
   </si>
   <si>
-    <t xml:space="preserve"> type</t>
-  </si>
-  <si>
-    <t>idA</t>
-  </si>
-  <si>
-    <t>idC</t>
-  </si>
-  <si>
-    <t>idConv</t>
-  </si>
-  <si>
     <t xml:space="preserve"> Allergie au gluten</t>
   </si>
   <si>
-    <t>ALLERGENE</t>
-  </si>
-  <si>
     <t>Intolérance au lactose</t>
   </si>
   <si>
@@ -1342,18 +1296,12 @@
     <t xml:space="preserve">Régime végétarien </t>
   </si>
   <si>
-    <t>CROYANCE</t>
-  </si>
-  <si>
     <t>Interdiction de porc</t>
   </si>
   <si>
     <t xml:space="preserve">Refus de friture          </t>
   </si>
   <si>
-    <t>CONVICTION</t>
-  </si>
-  <si>
     <t xml:space="preserve">  Refus de viande industrielle</t>
   </si>
   <si>
@@ -1375,9 +1323,6 @@
     <t xml:space="preserve"> Pas de fromage fort</t>
   </si>
   <si>
-    <t xml:space="preserve">idA   </t>
-  </si>
-  <si>
     <t>allergenes</t>
   </si>
   <si>
@@ -1402,9 +1347,6 @@
     <t xml:space="preserve">  Végétarien</t>
   </si>
   <si>
-    <t xml:space="preserve"> Sans porc</t>
-  </si>
-  <si>
     <t>idS</t>
   </si>
   <si>
@@ -1436,6 +1378,66 @@
   </si>
   <si>
     <t>Sauce blanche</t>
+  </si>
+  <si>
+    <t>idContrainte</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> Religieux pratiquant</t>
+  </si>
+  <si>
+    <t>idT</t>
+  </si>
+  <si>
+    <t>Rite du Tender Suprême</t>
+  </si>
+  <si>
+    <t>Tomates</t>
+  </si>
+  <si>
+    <t>Ail</t>
+  </si>
+  <si>
+    <t>Oignon</t>
+  </si>
+  <si>
+    <t>Sel</t>
+  </si>
+  <si>
+    <t>Poivre</t>
+  </si>
+  <si>
+    <t>Piment</t>
+  </si>
+  <si>
+    <t>Huile</t>
+  </si>
+  <si>
+    <t>Oeufs</t>
+  </si>
+  <si>
+    <t>Vinaigre</t>
+  </si>
+  <si>
+    <t>Sucre</t>
+  </si>
+  <si>
+    <t>Crème</t>
+  </si>
+  <si>
+    <t>Fromage</t>
+  </si>
+  <si>
+    <t>Cornichons</t>
+  </si>
+  <si>
+    <t>Estragon</t>
+  </si>
+  <si>
+    <t>Citron</t>
+  </si>
+  <si>
+    <t>lieu</t>
   </si>
 </sst>
 </file>
@@ -1444,7 +1446,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0#&quot; &quot;##&quot; &quot;##&quot; &quot;##&quot; &quot;##"/>
-    <numFmt numFmtId="166" formatCode="dd/mm/yy;@"/>
+    <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
   <fonts count="9">
     <font>
@@ -1496,14 +1498,15 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <charset val="1"/>
     </font>
   </fonts>
   <fills count="3">
@@ -1548,7 +1551,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1556,10 +1559,9 @@
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1567,6 +1569,13 @@
     <xf numFmtId="14" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" xr:uid="{00000000-000B-0000-0000-000008000000}"/>
@@ -1586,7 +1595,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Thème Office">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1882,8 +1891,8 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A6B9DE-762D-4CD8-9484-40200F975624}">
-  <dimension ref="A1:N52"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:M52"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
     <col min="4" max="4" width="31.28515625" customWidth="1"/>
@@ -1892,7 +1901,7 @@
     <col min="8" max="8" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1932,11 +1941,8 @@
       <c r="M1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14">
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1973,11 +1979,8 @@
       <c r="M2">
         <v>1</v>
       </c>
-      <c r="N2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14">
+    </row>
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>2</v>
       </c>
@@ -2008,11 +2011,8 @@
       <c r="K3">
         <v>1</v>
       </c>
-      <c r="N3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14">
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>3</v>
       </c>
@@ -2034,9 +2034,6 @@
       <c r="G4">
         <v>3</v>
       </c>
-      <c r="H4">
-        <v>8</v>
-      </c>
       <c r="I4">
         <v>2</v>
       </c>
@@ -2052,11 +2049,8 @@
       <c r="M4">
         <v>2</v>
       </c>
-      <c r="N4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14">
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5">
         <v>4</v>
       </c>
@@ -2084,11 +2078,8 @@
       <c r="J5">
         <v>1</v>
       </c>
-      <c r="N5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14">
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6">
         <v>5</v>
       </c>
@@ -2119,11 +2110,8 @@
       <c r="L6">
         <v>1</v>
       </c>
-      <c r="N6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14">
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7">
         <v>6</v>
       </c>
@@ -2154,11 +2142,8 @@
       <c r="K7">
         <v>1</v>
       </c>
-      <c r="N7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14">
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8">
         <v>7</v>
       </c>
@@ -2180,9 +2165,6 @@
       <c r="G8">
         <v>3</v>
       </c>
-      <c r="H8">
-        <v>7</v>
-      </c>
       <c r="I8">
         <v>3</v>
       </c>
@@ -2198,11 +2180,8 @@
       <c r="M8">
         <v>1</v>
       </c>
-      <c r="N8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14">
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9">
         <v>8</v>
       </c>
@@ -2224,9 +2203,6 @@
       <c r="G9">
         <v>2</v>
       </c>
-      <c r="H9">
-        <v>4</v>
-      </c>
       <c r="I9">
         <v>1</v>
       </c>
@@ -2242,11 +2218,8 @@
       <c r="M9">
         <v>2</v>
       </c>
-      <c r="N9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14">
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10">
         <v>9</v>
       </c>
@@ -2283,11 +2256,8 @@
       <c r="M10">
         <v>3</v>
       </c>
-      <c r="N10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14">
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2324,11 +2294,8 @@
       <c r="M11">
         <v>3</v>
       </c>
-      <c r="N11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14">
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2359,11 +2326,8 @@
       <c r="K12">
         <v>1</v>
       </c>
-      <c r="N12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14">
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2391,11 +2355,8 @@
       <c r="J13">
         <v>1</v>
       </c>
-      <c r="N13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:14">
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2426,11 +2387,8 @@
       <c r="L14">
         <v>1</v>
       </c>
-      <c r="N14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:14">
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2467,11 +2425,8 @@
       <c r="M15">
         <v>1</v>
       </c>
-      <c r="N15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14">
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2508,11 +2463,8 @@
       <c r="M16">
         <v>2</v>
       </c>
-      <c r="N16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14">
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2549,11 +2501,8 @@
       <c r="M17">
         <v>1</v>
       </c>
-      <c r="N17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14">
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2584,11 +2533,8 @@
       <c r="K18">
         <v>1</v>
       </c>
-      <c r="N18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14">
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2616,11 +2562,8 @@
       <c r="J19">
         <v>1</v>
       </c>
-      <c r="N19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14">
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2651,11 +2594,8 @@
       <c r="L20">
         <v>1</v>
       </c>
-      <c r="N20">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14">
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2677,9 +2617,6 @@
       <c r="G21">
         <v>2</v>
       </c>
-      <c r="H21">
-        <v>5</v>
-      </c>
       <c r="I21">
         <v>1</v>
       </c>
@@ -2695,11 +2632,8 @@
       <c r="M21">
         <v>1</v>
       </c>
-      <c r="N21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14">
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2730,11 +2664,8 @@
       <c r="K22">
         <v>1</v>
       </c>
-      <c r="N22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14">
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2768,11 +2699,8 @@
       <c r="L23">
         <v>1</v>
       </c>
-      <c r="N23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14">
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2803,11 +2731,8 @@
       <c r="L24">
         <v>2</v>
       </c>
-      <c r="N24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14">
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2838,11 +2763,8 @@
       <c r="K25">
         <v>1</v>
       </c>
-      <c r="N25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14">
+    </row>
+    <row r="26" spans="1:13">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2864,9 +2786,6 @@
       <c r="G26">
         <v>4</v>
       </c>
-      <c r="H26">
-        <v>1</v>
-      </c>
       <c r="I26">
         <v>3</v>
       </c>
@@ -2882,11 +2801,8 @@
       <c r="M26">
         <v>1</v>
       </c>
-      <c r="N26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14">
+    </row>
+    <row r="27" spans="1:13">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2923,11 +2839,8 @@
       <c r="M27">
         <v>2</v>
       </c>
-      <c r="N27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14">
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2949,9 +2862,6 @@
       <c r="G28">
         <v>3</v>
       </c>
-      <c r="H28">
-        <v>3</v>
-      </c>
       <c r="I28">
         <v>2</v>
       </c>
@@ -2967,11 +2877,8 @@
       <c r="M28">
         <v>3</v>
       </c>
-      <c r="N28">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14">
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29">
         <v>28</v>
       </c>
@@ -2993,9 +2900,6 @@
       <c r="G29">
         <v>2</v>
       </c>
-      <c r="H29">
-        <v>10</v>
-      </c>
       <c r="I29">
         <v>3</v>
       </c>
@@ -3011,11 +2915,8 @@
       <c r="M29">
         <v>1</v>
       </c>
-      <c r="N29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14">
+    </row>
+    <row r="30" spans="1:13">
       <c r="A30">
         <v>29</v>
       </c>
@@ -3046,11 +2947,8 @@
       <c r="K30">
         <v>1</v>
       </c>
-      <c r="N30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14">
+    </row>
+    <row r="31" spans="1:13">
       <c r="A31">
         <v>30</v>
       </c>
@@ -3078,11 +2976,8 @@
       <c r="J31">
         <v>1</v>
       </c>
-      <c r="N31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14">
+    </row>
+    <row r="32" spans="1:13">
       <c r="A32">
         <v>31</v>
       </c>
@@ -3113,11 +3008,8 @@
       <c r="L32">
         <v>1</v>
       </c>
-      <c r="N32">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14">
+    </row>
+    <row r="33" spans="1:13">
       <c r="A33">
         <v>32</v>
       </c>
@@ -3151,11 +3043,8 @@
       <c r="L33">
         <v>2</v>
       </c>
-      <c r="N33">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14">
+    </row>
+    <row r="34" spans="1:13">
       <c r="A34">
         <v>33</v>
       </c>
@@ -3192,11 +3081,8 @@
       <c r="M34">
         <v>1</v>
       </c>
-      <c r="N34">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14">
+    </row>
+    <row r="35" spans="1:13">
       <c r="A35">
         <v>34</v>
       </c>
@@ -3233,11 +3119,8 @@
       <c r="M35">
         <v>2</v>
       </c>
-      <c r="N35">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14">
+    </row>
+    <row r="36" spans="1:13">
       <c r="A36">
         <v>35</v>
       </c>
@@ -3274,11 +3157,8 @@
       <c r="M36">
         <v>1</v>
       </c>
-      <c r="N36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:14">
+    </row>
+    <row r="37" spans="1:13">
       <c r="A37">
         <v>36</v>
       </c>
@@ -3309,11 +3189,8 @@
       <c r="K37">
         <v>1</v>
       </c>
-      <c r="N37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14">
+    </row>
+    <row r="38" spans="1:13">
       <c r="A38">
         <v>37</v>
       </c>
@@ -3344,11 +3221,8 @@
       <c r="L38">
         <v>1</v>
       </c>
-      <c r="N38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14">
+    </row>
+    <row r="39" spans="1:13">
       <c r="A39">
         <v>38</v>
       </c>
@@ -3376,11 +3250,8 @@
       <c r="J39">
         <v>1</v>
       </c>
-      <c r="N39">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:14">
+    </row>
+    <row r="40" spans="1:13">
       <c r="A40">
         <v>39</v>
       </c>
@@ -3417,11 +3288,8 @@
       <c r="M40">
         <v>1</v>
       </c>
-      <c r="N40">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:14">
+    </row>
+    <row r="41" spans="1:13">
       <c r="A41">
         <v>40</v>
       </c>
@@ -3443,9 +3311,6 @@
       <c r="G41">
         <v>2</v>
       </c>
-      <c r="H41">
-        <v>6</v>
-      </c>
       <c r="I41">
         <v>3</v>
       </c>
@@ -3461,11 +3326,8 @@
       <c r="M41">
         <v>3</v>
       </c>
-      <c r="N41">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:14">
+    </row>
+    <row r="42" spans="1:13">
       <c r="A42">
         <v>41</v>
       </c>
@@ -3499,11 +3361,8 @@
       <c r="L42">
         <v>1</v>
       </c>
-      <c r="N42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:14">
+    </row>
+    <row r="43" spans="1:13">
       <c r="A43">
         <v>42</v>
       </c>
@@ -3531,11 +3390,8 @@
       <c r="J43">
         <v>2</v>
       </c>
-      <c r="N43">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:14">
+    </row>
+    <row r="44" spans="1:13">
       <c r="A44">
         <v>43</v>
       </c>
@@ -3563,11 +3419,8 @@
       <c r="J44">
         <v>1</v>
       </c>
-      <c r="N44">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:14">
+    </row>
+    <row r="45" spans="1:13">
       <c r="A45">
         <v>44</v>
       </c>
@@ -3604,11 +3457,8 @@
       <c r="M45">
         <v>2</v>
       </c>
-      <c r="N45">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:14">
+    </row>
+    <row r="46" spans="1:13">
       <c r="A46">
         <v>45</v>
       </c>
@@ -3645,11 +3495,8 @@
       <c r="M46">
         <v>1</v>
       </c>
-      <c r="N46">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:14">
+    </row>
+    <row r="47" spans="1:13">
       <c r="A47">
         <v>46</v>
       </c>
@@ -3671,9 +3518,6 @@
       <c r="G47">
         <v>1</v>
       </c>
-      <c r="H47">
-        <v>2</v>
-      </c>
       <c r="I47">
         <v>1</v>
       </c>
@@ -3689,11 +3533,8 @@
       <c r="M47">
         <v>3</v>
       </c>
-      <c r="N47">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:14">
+    </row>
+    <row r="48" spans="1:13">
       <c r="A48">
         <v>47</v>
       </c>
@@ -3724,11 +3565,8 @@
       <c r="K48">
         <v>1</v>
       </c>
-      <c r="N48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:14">
+    </row>
+    <row r="49" spans="1:13">
       <c r="A49">
         <v>48</v>
       </c>
@@ -3759,11 +3597,8 @@
       <c r="L49">
         <v>2</v>
       </c>
-      <c r="N49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:14">
+    </row>
+    <row r="50" spans="1:13">
       <c r="A50">
         <v>49</v>
       </c>
@@ -3791,11 +3626,8 @@
       <c r="J50">
         <v>1</v>
       </c>
-      <c r="N50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:14">
+    </row>
+    <row r="51" spans="1:13">
       <c r="A51">
         <v>50</v>
       </c>
@@ -3829,11 +3661,8 @@
       <c r="L51">
         <v>1</v>
       </c>
-      <c r="N51">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:14" ht="15.75">
+    </row>
+    <row r="52" spans="1:13" ht="15.75">
       <c r="A52">
         <v>51</v>
       </c>
@@ -3855,9 +3684,6 @@
       <c r="G52">
         <v>10</v>
       </c>
-      <c r="H52">
-        <v>9</v>
-      </c>
       <c r="I52">
         <v>3</v>
       </c>
@@ -3872,9 +3698,6 @@
       </c>
       <c r="M52">
         <v>3</v>
-      </c>
-      <c r="N52">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3882,13 +3705,141 @@
     <hyperlink ref="D52" r:id="rId1" xr:uid="{1DD768BE-DBC1-4FE8-9019-F0337C5A92E4}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221443EF-5CAA-4D8F-99E0-E1F7C9868982}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7368821-A8B6-4663-8B70-AAC06AB66366}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B1" t="s">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>318</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7938516-E6BC-46F7-BFB9-9A46C4854A04}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE11920-A5FA-41BA-B201-1543B4434A54}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34.140625" customWidth="1"/>
   </cols>
@@ -3898,13 +3849,13 @@
         <v>13</v>
       </c>
       <c r="B1" t="s">
-        <v>5</v>
+        <v>457</v>
       </c>
       <c r="C1" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="D1" t="s">
-        <v>328</v>
+        <v>7</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -3912,13 +3863,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="C2" s="3">
         <v>46035</v>
       </c>
       <c r="D2">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -3926,13 +3877,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="C3" s="3">
         <v>46066</v>
       </c>
       <c r="D3">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -3940,13 +3891,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C4" s="3">
         <v>46094</v>
       </c>
       <c r="D4">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -3954,13 +3905,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C5" s="3">
         <v>46155</v>
       </c>
       <c r="D5">
-        <v>4</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -3968,13 +3919,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="C6" s="3">
         <v>46155</v>
       </c>
       <c r="D6">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -3982,13 +3933,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="C7" s="3">
         <v>46216</v>
       </c>
       <c r="D7">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -3996,13 +3947,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C8" s="3">
         <v>46278</v>
       </c>
       <c r="D8">
-        <v>7</v>
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -4010,13 +3961,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>335</v>
+        <v>331</v>
       </c>
       <c r="C9" s="3">
         <v>46308</v>
       </c>
       <c r="D9">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -4024,13 +3975,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="C10" s="3">
         <v>46339</v>
       </c>
       <c r="D10">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -4038,13 +3989,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>334</v>
+        <v>330</v>
       </c>
       <c r="C11" s="3">
         <v>46369</v>
       </c>
       <c r="D11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4052,10 +4003,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8593E13-AF45-4F25-87C1-268A620169C2}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="42.28515625" customWidth="1"/>
     <col min="3" max="3" width="9.5703125" customWidth="1"/>
@@ -4063,13 +4014,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="B1" t="s">
-        <v>336</v>
+        <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>337</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -4077,10 +4028,10 @@
         <v>1</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="C2" s="8">
-        <v>7</v>
+        <v>333</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -4088,9 +4039,9 @@
         <v>2</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="C3" s="8">
+        <v>334</v>
+      </c>
+      <c r="C3">
         <v>2</v>
       </c>
     </row>
@@ -4099,10 +4050,10 @@
         <v>3</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="C4" s="8">
-        <v>10</v>
+        <v>335</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -4110,9 +4061,9 @@
         <v>4</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="C5" s="8">
+        <v>336</v>
+      </c>
+      <c r="C5">
         <v>4</v>
       </c>
     </row>
@@ -4121,10 +4072,10 @@
         <v>5</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>342</v>
-      </c>
-      <c r="C6" s="8">
-        <v>1</v>
+        <v>337</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:3">
@@ -4132,10 +4083,10 @@
         <v>6</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>343</v>
-      </c>
-      <c r="C7" s="8">
-        <v>9</v>
+        <v>338</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:3">
@@ -4143,10 +4094,10 @@
         <v>7</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>344</v>
-      </c>
-      <c r="C8" s="8">
-        <v>6</v>
+        <v>339</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:3">
@@ -4154,21 +4105,21 @@
         <v>8</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>345</v>
-      </c>
-      <c r="C9" s="8">
-        <v>11</v>
+        <v>340</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="9" t="s">
-        <v>346</v>
+      <c r="B10" s="15" t="s">
+        <v>441</v>
       </c>
       <c r="C10">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -4176,10 +4127,10 @@
         <v>10</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>347</v>
-      </c>
-      <c r="C11" s="8">
-        <v>3</v>
+        <v>341</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -4187,20 +4138,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7736852-B5A3-4EA0-90D7-EE45E8F34F53}">
-  <dimension ref="A1:B23"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="25.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="B1" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -4208,7 +4159,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -4216,7 +4167,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -4224,7 +4175,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -4232,7 +4183,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -4240,7 +4191,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -4248,7 +4199,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -4256,7 +4207,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -4264,7 +4215,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -4272,7 +4223,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
     </row>
     <row r="11" spans="1:2">
@@ -4280,7 +4231,7 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
     </row>
     <row r="12" spans="1:2">
@@ -4288,7 +4239,7 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
     </row>
     <row r="13" spans="1:2">
@@ -4296,7 +4247,7 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
     </row>
     <row r="14" spans="1:2">
@@ -4304,7 +4255,7 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
     </row>
     <row r="15" spans="1:2">
@@ -4312,7 +4263,7 @@
         <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
     </row>
     <row r="16" spans="1:2">
@@ -4320,7 +4271,7 @@
         <v>16</v>
       </c>
       <c r="B16" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
     </row>
     <row r="17" spans="1:2">
@@ -4328,7 +4279,7 @@
         <v>17</v>
       </c>
       <c r="B17" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
     </row>
     <row r="18" spans="1:2">
@@ -4336,7 +4287,7 @@
         <v>18</v>
       </c>
       <c r="B18" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
     </row>
     <row r="19" spans="1:2">
@@ -4344,7 +4295,7 @@
         <v>19</v>
       </c>
       <c r="B19" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
     </row>
     <row r="20" spans="1:2">
@@ -4352,7 +4303,7 @@
         <v>20</v>
       </c>
       <c r="B20" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
     <row r="21" spans="1:2">
@@ -4360,7 +4311,7 @@
         <v>21</v>
       </c>
       <c r="B21" t="s">
-        <v>369</v>
+        <v>363</v>
       </c>
     </row>
     <row r="22" spans="1:2">
@@ -4368,7 +4319,7 @@
         <v>22</v>
       </c>
       <c r="B22" t="s">
-        <v>370</v>
+        <v>364</v>
       </c>
     </row>
     <row r="23" spans="1:2">
@@ -4376,7 +4327,143 @@
         <v>23</v>
       </c>
       <c r="B23" t="s">
-        <v>371</v>
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="16">
+        <v>24</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="16">
+        <v>25</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="16">
+        <v>26</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="16">
+        <v>27</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="16">
+        <v>28</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>435</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="16">
+        <v>29</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="16">
+        <v>30</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="16">
+        <v>31</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="16">
+        <v>32</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="16">
+        <v>33</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="16">
+        <v>34</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="16">
+        <v>35</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="16">
+        <v>36</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="16">
+        <v>37</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="16">
+        <v>38</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="16">
+        <v>39</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="16">
+        <v>40</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
@@ -4387,100 +4474,52 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DDB049-21B5-47C8-B1CC-963F1F30C6BC}">
-  <dimension ref="A1:C8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="3" max="3" width="13.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:1">
       <c r="A1" t="s">
-        <v>372</v>
-      </c>
-      <c r="B1" t="s">
-        <v>373</v>
-      </c>
-      <c r="C1" t="s">
-        <v>374</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+    </row>
+    <row r="3" spans="1:1">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+    </row>
+    <row r="4" spans="1:1">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+    </row>
+    <row r="5" spans="1:1">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+    </row>
+    <row r="6" spans="1:1">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+    </row>
+    <row r="7" spans="1:1">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+    </row>
+    <row r="8" spans="1:1">
       <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
         <v>11</v>
-      </c>
-      <c r="C8" t="s">
-        <v>360</v>
       </c>
     </row>
   </sheetData>
@@ -4488,145 +4527,181 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476A76D1-5D51-4DFB-BE48-DD996E1824BF}">
-  <dimension ref="A1:C12"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <dimension ref="A1:D12"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="72.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
+    <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B1" t="s">
-        <v>375</v>
+        <v>367</v>
       </c>
       <c r="C1" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
+        <v>368</v>
+      </c>
+      <c r="D1" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>377</v>
+        <v>369</v>
       </c>
       <c r="C2" t="s">
-        <v>378</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
+        <v>370</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>379</v>
+        <v>371</v>
       </c>
       <c r="C3" t="s">
-        <v>380</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
+        <v>372</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>381</v>
+        <v>373</v>
       </c>
       <c r="C4" t="s">
-        <v>382</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
+        <v>374</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>383</v>
+        <v>375</v>
       </c>
       <c r="C5" t="s">
-        <v>384</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
+        <v>376</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>385</v>
+        <v>377</v>
       </c>
       <c r="C6" t="s">
-        <v>386</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
+        <v>378</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
       <c r="A7">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>387</v>
+        <v>379</v>
       </c>
       <c r="C7" t="s">
-        <v>388</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
+        <v>380</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
       <c r="A8">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>389</v>
+        <v>381</v>
       </c>
       <c r="C8" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
+        <v>382</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
       <c r="A9">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>391</v>
+        <v>383</v>
       </c>
       <c r="C9" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
+        <v>384</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
       <c r="A10">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>393</v>
+        <v>385</v>
       </c>
       <c r="C10" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
+        <v>386</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
       <c r="A11">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>340</v>
+        <v>335</v>
       </c>
       <c r="C11" t="s">
-        <v>395</v>
-      </c>
-    </row>
-    <row r="12" spans="1:3">
+        <v>387</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
       <c r="A12">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>396</v>
+        <v>388</v>
       </c>
       <c r="C12" t="s">
-        <v>397</v>
+        <v>389</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -4634,17 +4709,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A29A99-C4C2-4014-887E-65B5C0B9BBF8}">
   <dimension ref="A1:B47"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B1" t="s">
-        <v>373</v>
+        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5020,10 +5095,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40FC11C4-9A11-45A3-B059-AA1A3BE2A68F}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="17.7109375" customWidth="1"/>
     <col min="3" max="3" width="16.85546875" customWidth="1"/>
@@ -5031,13 +5106,13 @@
   <sheetData>
     <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>398</v>
+        <v>390</v>
       </c>
       <c r="B1" t="s">
-        <v>399</v>
+        <v>391</v>
       </c>
       <c r="C1" t="s">
-        <v>400</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:3">
@@ -5045,10 +5120,10 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>401</v>
+        <v>393</v>
       </c>
       <c r="C2" t="s">
-        <v>402</v>
+        <v>394</v>
       </c>
     </row>
     <row r="3" spans="1:3">
@@ -5056,10 +5131,10 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>403</v>
+        <v>395</v>
       </c>
       <c r="C3" t="s">
-        <v>404</v>
+        <v>396</v>
       </c>
     </row>
     <row r="4" spans="1:3">
@@ -5067,10 +5142,10 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>405</v>
+        <v>397</v>
       </c>
       <c r="C4" t="s">
-        <v>406</v>
+        <v>398</v>
       </c>
     </row>
     <row r="5" spans="1:3">
@@ -5078,10 +5153,10 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>407</v>
+        <v>399</v>
       </c>
       <c r="C5" t="s">
-        <v>408</v>
+        <v>400</v>
       </c>
     </row>
   </sheetData>
@@ -5089,17 +5164,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DCE8B9-25EF-4A25-8908-BEA8D48F1D2F}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A125E296-0ECF-4112-ADE5-29F81271894B}">
+  <dimension ref="A1:B71"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>337</v>
+        <v>440</v>
       </c>
       <c r="B1" t="s">
-        <v>398</v>
+        <v>13</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5115,12 +5190,12 @@
         <v>1</v>
       </c>
       <c r="B3">
-        <v>2</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="B4">
         <v>2</v>
@@ -5128,114 +5203,538 @@
     </row>
     <row r="5" spans="1:2">
       <c r="A5">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="B5">
-        <v>3</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="B6">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="B7">
-        <v>3</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B8">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:2">
       <c r="A9">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B9">
-        <v>2</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10" spans="1:2">
       <c r="A10">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B10">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="11" spans="1:2">
       <c r="A11">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B11">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12" spans="1:2">
       <c r="A12">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="B12">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13" spans="1:2">
       <c r="A13">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B13">
-        <v>1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:2">
       <c r="A14">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="B14">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="15" spans="1:2">
       <c r="A15">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="B15">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="16" spans="1:2">
       <c r="A16">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B16">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="17" spans="1:2">
       <c r="A17">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="B17">
-        <v>2</v>
+        <v>8</v>
       </c>
     </row>
     <row r="18" spans="1:2">
       <c r="A18">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="B18">
-        <v>2</v>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>18</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>19</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>20</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>22</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>22</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>22</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>22</v>
+      </c>
+      <c r="B33">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>22</v>
+      </c>
+      <c r="B34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>23</v>
+      </c>
+      <c r="B35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>28</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>28</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>28</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>29</v>
+      </c>
+      <c r="B39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>30</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>31</v>
+      </c>
+      <c r="B41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>31</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>33</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>34</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>35</v>
+      </c>
+      <c r="B45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>37</v>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>37</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>37</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>39</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>39</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>40</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>40</v>
+      </c>
+      <c r="B52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>40</v>
+      </c>
+      <c r="B53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>40</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>41</v>
+      </c>
+      <c r="B55">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>41</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>42</v>
+      </c>
+      <c r="B57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>43</v>
+      </c>
+      <c r="B58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>43</v>
+      </c>
+      <c r="B59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>43</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>44</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>45</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>45</v>
+      </c>
+      <c r="B63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>45</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>46</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>47</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>47</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>48</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>51</v>
+      </c>
+      <c r="B69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>51</v>
+      </c>
+      <c r="B70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>51</v>
+      </c>
+      <c r="B71">
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -5243,138 +5742,292 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DCE8B9-25EF-4A25-8908-BEA8D48F1D2F}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>9</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35096018-BB9E-4928-A341-4382324C36A0}">
   <dimension ref="A1:D9"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="4" max="4" width="12" style="7" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>409</v>
-      </c>
-      <c r="B1" t="s">
-        <v>398</v>
+        <v>401</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>323</v>
       </c>
       <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="7" t="s">
-        <v>327</v>
+        <v>440</v>
+      </c>
+      <c r="D1" t="s">
+        <v>390</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
+      <c r="B2" s="7">
+        <v>45425</v>
       </c>
       <c r="C2">
         <v>9</v>
       </c>
-      <c r="D2" s="7">
-        <v>45425</v>
+      <c r="D2">
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
+      <c r="B3" s="7">
+        <v>45553</v>
       </c>
       <c r="C3">
         <v>10</v>
       </c>
-      <c r="D3" s="7">
-        <v>45553</v>
+      <c r="D3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>3</v>
+      <c r="B4" s="7">
+        <v>45626</v>
       </c>
       <c r="C4">
         <v>27</v>
       </c>
-      <c r="D4" s="7">
-        <v>45626</v>
+      <c r="D4">
+        <v>3</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>4</v>
+      <c r="B5" s="7">
+        <v>45718</v>
       </c>
       <c r="C5">
         <v>40</v>
       </c>
-      <c r="D5" s="7">
-        <v>45718</v>
+      <c r="D5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>1</v>
+      <c r="B6" s="7">
+        <v>45823</v>
       </c>
       <c r="C6">
         <v>51</v>
       </c>
-      <c r="D6" s="7">
-        <v>45823</v>
+      <c r="D6">
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>2</v>
+      <c r="B7" s="7">
+        <v>45880</v>
       </c>
       <c r="C7">
         <v>47</v>
       </c>
-      <c r="D7" s="7">
-        <v>45880</v>
+      <c r="D7">
+        <v>2</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>3</v>
+      <c r="B8" s="7">
+        <v>45948</v>
       </c>
       <c r="C8">
         <v>26</v>
       </c>
-      <c r="D8" s="7">
-        <v>45948</v>
+      <c r="D8">
+        <v>3</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>4</v>
+      <c r="B9" s="7">
+        <v>46005</v>
       </c>
       <c r="C9">
         <v>44</v>
       </c>
-      <c r="D9" s="7">
-        <v>46005</v>
+      <c r="D9">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
@@ -5382,20 +6035,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE918DF-2E53-4F94-B75B-28FE1A378FE7}">
   <dimension ref="A1:B24"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="10" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>410</v>
+        <v>402</v>
       </c>
       <c r="B1" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -5418,7 +6071,7 @@
       <c r="A4">
         <v>1</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>16</v>
       </c>
     </row>
@@ -5587,1774 +6240,141 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE8F9A9-A487-4868-AFA4-BF0B3BE731BD}">
-  <dimension ref="A1:J56"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C246EE82-FCA8-4617-A366-829003F780A5}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="3" max="3" width="15.85546875" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" customWidth="1"/>
-    <col min="7" max="7" width="14.28515625" customWidth="1"/>
-    <col min="8" max="8" width="21" customWidth="1"/>
-    <col min="9" max="9" width="22.42578125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="12.85546875" customWidth="1"/>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
-        <v>215</v>
+        <v>403</v>
       </c>
       <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>216</v>
-      </c>
-      <c r="D1" t="s">
-        <v>217</v>
-      </c>
-      <c r="E1" t="s">
-        <v>7</v>
-      </c>
-      <c r="F1" t="s">
-        <v>8</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>218</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>219</v>
-      </c>
-      <c r="J1" s="14" t="s">
-        <v>220</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-      <c r="C2" s="12" t="s">
-        <v>221</v>
-      </c>
-      <c r="D2" t="s">
-        <v>14</v>
-      </c>
-      <c r="E2">
-        <v>1</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-      <c r="H2" t="s">
-        <v>222</v>
-      </c>
-      <c r="I2" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J2" s="13">
-        <v>45297</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10">
+      <c r="B2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C2" s="9"/>
+    </row>
+    <row r="3" spans="1:3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-      <c r="C3" s="12" t="s">
-        <v>223</v>
-      </c>
-      <c r="D3" t="s">
-        <v>18</v>
-      </c>
-      <c r="E3">
-        <v>7</v>
-      </c>
-      <c r="G3">
-        <v>1</v>
-      </c>
-      <c r="H3" t="s">
-        <v>222</v>
-      </c>
-      <c r="I3" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J3" s="13">
-        <v>45310</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10">
+      <c r="B3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4">
-        <v>3</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D4" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4">
-        <v>8</v>
-      </c>
-      <c r="F4">
-        <v>2</v>
-      </c>
-      <c r="G4">
-        <v>3</v>
-      </c>
-      <c r="H4" t="s">
-        <v>225</v>
-      </c>
-      <c r="I4" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J4" s="13">
-        <v>45325</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10">
+      <c r="B4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>226</v>
-      </c>
-      <c r="D5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E5">
-        <v>10</v>
-      </c>
-      <c r="G5">
-        <v>2</v>
-      </c>
-      <c r="H5" t="s">
-        <v>227</v>
-      </c>
-      <c r="I5" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J5" s="13">
-        <v>45349</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10">
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>228</v>
-      </c>
-      <c r="D6" t="s">
-        <v>30</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-      <c r="G6">
-        <v>1</v>
-      </c>
-      <c r="H6" t="s">
-        <v>222</v>
-      </c>
-      <c r="I6" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J6" s="13">
-        <v>45362</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10">
+      <c r="B6" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7">
-        <v>6</v>
-      </c>
-      <c r="C7" s="12" t="s">
-        <v>229</v>
-      </c>
-      <c r="D7" t="s">
-        <v>34</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-      <c r="G7">
-        <v>1</v>
-      </c>
-      <c r="H7" t="s">
-        <v>222</v>
-      </c>
-      <c r="I7" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J7" s="13">
-        <v>45380</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10">
+      <c r="B7" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>230</v>
-      </c>
-      <c r="D8" t="s">
-        <v>38</v>
-      </c>
-      <c r="E8">
-        <v>7</v>
-      </c>
-      <c r="F8">
-        <v>3</v>
-      </c>
-      <c r="G8">
-        <v>3</v>
-      </c>
-      <c r="H8" t="s">
-        <v>225</v>
-      </c>
-      <c r="I8" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J8" s="13">
-        <v>45389</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10">
+      <c r="B8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-      <c r="C9" s="12" t="s">
-        <v>231</v>
-      </c>
-      <c r="D9" t="s">
-        <v>42</v>
-      </c>
-      <c r="E9">
-        <v>4</v>
-      </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9">
-        <v>2</v>
-      </c>
-      <c r="H9" t="s">
-        <v>227</v>
-      </c>
-      <c r="I9" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J9" s="13">
-        <v>45400</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10">
+      <c r="B9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10">
-        <v>9</v>
-      </c>
-      <c r="C10" s="12" t="s">
-        <v>232</v>
-      </c>
-      <c r="D10" t="s">
-        <v>46</v>
-      </c>
-      <c r="E10">
-        <v>1</v>
-      </c>
-      <c r="G10">
-        <v>1</v>
-      </c>
-      <c r="H10" t="s">
-        <v>222</v>
-      </c>
-      <c r="I10" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J10" s="13">
-        <v>45414</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>10</v>
-      </c>
-      <c r="C11" s="12" t="s">
-        <v>233</v>
-      </c>
-      <c r="D11" t="s">
-        <v>50</v>
-      </c>
-      <c r="E11">
-        <v>2</v>
-      </c>
-      <c r="G11">
-        <v>1</v>
-      </c>
-      <c r="H11" t="s">
-        <v>222</v>
-      </c>
-      <c r="I11" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J11" s="13">
-        <v>45433</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12">
-        <v>11</v>
-      </c>
-      <c r="C12" s="12" t="s">
-        <v>234</v>
-      </c>
-      <c r="D12" t="s">
-        <v>54</v>
-      </c>
-      <c r="E12">
-        <v>8</v>
-      </c>
-      <c r="G12">
-        <v>3</v>
-      </c>
-      <c r="H12" t="s">
-        <v>225</v>
-      </c>
-      <c r="I12" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J12" s="13">
-        <v>45452</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13">
-        <v>12</v>
-      </c>
-      <c r="C13" s="12" t="s">
-        <v>235</v>
-      </c>
-      <c r="D13" t="s">
-        <v>58</v>
-      </c>
-      <c r="E13">
-        <v>5</v>
-      </c>
-      <c r="G13">
-        <v>2</v>
-      </c>
-      <c r="H13" t="s">
-        <v>227</v>
-      </c>
-      <c r="I13" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J13" s="13">
-        <v>45468</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10">
-      <c r="A14">
-        <v>13</v>
-      </c>
-      <c r="B14">
-        <v>13</v>
-      </c>
-      <c r="C14" s="12" t="s">
-        <v>236</v>
-      </c>
-      <c r="D14" t="s">
-        <v>62</v>
-      </c>
-      <c r="E14">
-        <v>1</v>
-      </c>
-      <c r="G14">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>222</v>
-      </c>
-      <c r="I14" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J14" s="13">
-        <v>45477</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10">
-      <c r="A15">
-        <v>14</v>
-      </c>
-      <c r="B15">
-        <v>14</v>
-      </c>
-      <c r="C15" s="12" t="s">
-        <v>237</v>
-      </c>
-      <c r="D15" t="s">
-        <v>66</v>
-      </c>
-      <c r="E15">
-        <v>2</v>
-      </c>
-      <c r="G15">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>222</v>
-      </c>
-      <c r="I15" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J15" s="13">
-        <v>45492</v>
-      </c>
-    </row>
-    <row r="16" spans="1:10">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>15</v>
-      </c>
-      <c r="C16" s="12" t="s">
-        <v>238</v>
-      </c>
-      <c r="D16" t="s">
-        <v>70</v>
-      </c>
-      <c r="E16">
-        <v>6</v>
-      </c>
-      <c r="G16">
-        <v>3</v>
-      </c>
-      <c r="H16" t="s">
-        <v>225</v>
-      </c>
-      <c r="I16" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J16" s="13">
-        <v>45512</v>
-      </c>
-    </row>
-    <row r="17" spans="1:10">
-      <c r="A17">
-        <v>16</v>
-      </c>
-      <c r="B17">
-        <v>16</v>
-      </c>
-      <c r="C17" s="12" t="s">
-        <v>239</v>
-      </c>
-      <c r="D17" t="s">
-        <v>74</v>
-      </c>
-      <c r="E17">
-        <v>9</v>
-      </c>
-      <c r="G17">
-        <v>2</v>
-      </c>
-      <c r="H17" t="s">
-        <v>227</v>
-      </c>
-      <c r="I17" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J17" s="13">
-        <v>45527</v>
-      </c>
-    </row>
-    <row r="18" spans="1:10">
-      <c r="A18">
-        <v>17</v>
-      </c>
-      <c r="B18">
-        <v>17</v>
-      </c>
-      <c r="C18" s="12" t="s">
-        <v>240</v>
-      </c>
-      <c r="D18" t="s">
-        <v>78</v>
-      </c>
-      <c r="E18">
-        <v>1</v>
-      </c>
-      <c r="G18">
-        <v>1</v>
-      </c>
-      <c r="H18" t="s">
-        <v>222</v>
-      </c>
-      <c r="I18" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J18" s="13">
-        <v>45540</v>
-      </c>
-    </row>
-    <row r="19" spans="1:10">
-      <c r="A19">
-        <v>18</v>
-      </c>
-      <c r="B19">
-        <v>18</v>
-      </c>
-      <c r="C19" s="12" t="s">
-        <v>241</v>
-      </c>
-      <c r="D19" t="s">
-        <v>82</v>
-      </c>
-      <c r="E19">
-        <v>2</v>
-      </c>
-      <c r="G19">
-        <v>1</v>
-      </c>
-      <c r="H19" t="s">
-        <v>222</v>
-      </c>
-      <c r="I19" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J19" s="13">
-        <v>45552</v>
-      </c>
-    </row>
-    <row r="20" spans="1:10">
-      <c r="A20">
-        <v>19</v>
-      </c>
-      <c r="B20">
-        <v>19</v>
-      </c>
-      <c r="C20" s="12" t="s">
-        <v>242</v>
-      </c>
-      <c r="D20" t="s">
-        <v>86</v>
-      </c>
-      <c r="E20">
-        <v>10</v>
-      </c>
-      <c r="G20">
-        <v>3</v>
-      </c>
-      <c r="H20" t="s">
-        <v>225</v>
-      </c>
-      <c r="I20" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J20" s="13">
-        <v>45566</v>
-      </c>
-    </row>
-    <row r="21" spans="1:10">
-      <c r="A21">
-        <v>20</v>
-      </c>
-      <c r="B21">
-        <v>20</v>
-      </c>
-      <c r="C21" s="12" t="s">
-        <v>243</v>
-      </c>
-      <c r="D21" t="s">
-        <v>90</v>
-      </c>
-      <c r="E21">
-        <v>5</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21">
-        <v>2</v>
-      </c>
-      <c r="H21" t="s">
-        <v>227</v>
-      </c>
-      <c r="I21" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J21" s="13">
-        <v>45591</v>
-      </c>
-    </row>
-    <row r="22" spans="1:10">
-      <c r="A22">
-        <v>21</v>
-      </c>
-      <c r="B22">
-        <v>21</v>
-      </c>
-      <c r="C22" s="12" t="s">
-        <v>244</v>
-      </c>
-      <c r="D22" t="s">
-        <v>94</v>
-      </c>
-      <c r="E22">
-        <v>1</v>
-      </c>
-      <c r="G22">
-        <v>1</v>
-      </c>
-      <c r="H22" t="s">
-        <v>222</v>
-      </c>
-      <c r="I22" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J22" s="13">
-        <v>45602</v>
-      </c>
-    </row>
-    <row r="23" spans="1:10">
-      <c r="A23">
-        <v>22</v>
-      </c>
-      <c r="B23">
-        <v>22</v>
-      </c>
-      <c r="C23" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="D23" t="s">
-        <v>98</v>
-      </c>
-      <c r="E23">
-        <v>2</v>
-      </c>
-      <c r="G23">
-        <v>1</v>
-      </c>
-      <c r="H23" t="s">
-        <v>222</v>
-      </c>
-      <c r="I23" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J23" s="13">
-        <v>45614</v>
-      </c>
-    </row>
-    <row r="24" spans="1:10">
-      <c r="A24">
-        <v>23</v>
-      </c>
-      <c r="B24">
-        <v>23</v>
-      </c>
-      <c r="C24" s="12" t="s">
-        <v>246</v>
-      </c>
-      <c r="D24" t="s">
-        <v>102</v>
-      </c>
-      <c r="E24">
-        <v>8</v>
-      </c>
-      <c r="G24">
-        <v>3</v>
-      </c>
-      <c r="H24" t="s">
-        <v>225</v>
-      </c>
-      <c r="I24" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J24" s="13">
-        <v>45629</v>
-      </c>
-    </row>
-    <row r="25" spans="1:10">
-      <c r="A25">
-        <v>24</v>
-      </c>
-      <c r="B25">
-        <v>24</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>247</v>
-      </c>
-      <c r="D25" t="s">
-        <v>106</v>
-      </c>
-      <c r="E25">
-        <v>4</v>
-      </c>
-      <c r="G25">
-        <v>2</v>
-      </c>
-      <c r="H25" t="s">
-        <v>227</v>
-      </c>
-      <c r="I25" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J25" s="13">
-        <v>45647</v>
-      </c>
-    </row>
-    <row r="26" spans="1:10">
-      <c r="A26">
-        <v>25</v>
-      </c>
-      <c r="B26">
-        <v>25</v>
-      </c>
-      <c r="C26" s="12" t="s">
-        <v>248</v>
-      </c>
-      <c r="D26" t="s">
-        <v>110</v>
-      </c>
-      <c r="E26">
-        <v>1</v>
-      </c>
-      <c r="F26">
-        <v>3</v>
-      </c>
-      <c r="G26">
-        <v>4</v>
-      </c>
-      <c r="H26" t="s">
-        <v>249</v>
-      </c>
-      <c r="I26" s="1">
-        <v>55667788990033</v>
-      </c>
-      <c r="J26" s="13">
-        <v>45656</v>
-      </c>
-    </row>
-    <row r="27" spans="1:10">
-      <c r="A27">
-        <v>26</v>
-      </c>
-      <c r="B27">
-        <v>26</v>
-      </c>
-      <c r="C27" s="12" t="s">
-        <v>250</v>
-      </c>
-      <c r="D27" t="s">
-        <v>114</v>
-      </c>
-      <c r="E27">
-        <v>2</v>
-      </c>
-      <c r="G27">
-        <v>1</v>
-      </c>
-      <c r="H27" t="s">
-        <v>222</v>
-      </c>
-      <c r="I27" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J27" s="13">
-        <v>45662</v>
-      </c>
-    </row>
-    <row r="28" spans="1:10">
-      <c r="A28">
-        <v>27</v>
-      </c>
-      <c r="B28">
-        <v>27</v>
-      </c>
-      <c r="C28" s="12" t="s">
-        <v>251</v>
-      </c>
-      <c r="D28" t="s">
-        <v>118</v>
-      </c>
-      <c r="E28">
-        <v>3</v>
-      </c>
-      <c r="F28">
-        <v>2</v>
-      </c>
-      <c r="G28">
-        <v>3</v>
-      </c>
-      <c r="H28" t="s">
-        <v>225</v>
-      </c>
-      <c r="I28" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J28" s="13">
-        <v>45679</v>
-      </c>
-    </row>
-    <row r="29" spans="1:10">
-      <c r="A29">
-        <v>28</v>
-      </c>
-      <c r="B29">
-        <v>28</v>
-      </c>
-      <c r="C29" s="12" t="s">
-        <v>252</v>
-      </c>
-      <c r="D29" t="s">
-        <v>122</v>
-      </c>
-      <c r="E29">
-        <v>10</v>
-      </c>
-      <c r="F29">
-        <v>3</v>
-      </c>
-      <c r="G29">
-        <v>2</v>
-      </c>
-      <c r="H29" t="s">
-        <v>227</v>
-      </c>
-      <c r="I29" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J29" s="13">
-        <v>45698</v>
-      </c>
-    </row>
-    <row r="30" spans="1:10">
-      <c r="A30">
-        <v>29</v>
-      </c>
-      <c r="B30">
-        <v>29</v>
-      </c>
-      <c r="C30" s="12" t="s">
-        <v>253</v>
-      </c>
-      <c r="D30" t="s">
-        <v>125</v>
-      </c>
-      <c r="E30">
-        <v>10</v>
-      </c>
-      <c r="G30">
-        <v>1</v>
-      </c>
-      <c r="H30" t="s">
-        <v>222</v>
-      </c>
-      <c r="I30" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J30" s="13">
-        <v>45712</v>
-      </c>
-    </row>
-    <row r="31" spans="1:10">
-      <c r="A31">
-        <v>30</v>
-      </c>
-      <c r="B31">
-        <v>30</v>
-      </c>
-      <c r="C31" s="12" t="s">
-        <v>254</v>
-      </c>
-      <c r="D31" t="s">
-        <v>129</v>
-      </c>
-      <c r="E31">
-        <v>2</v>
-      </c>
-      <c r="G31">
-        <v>1</v>
-      </c>
-      <c r="H31" t="s">
-        <v>222</v>
-      </c>
-      <c r="I31" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J31" s="13">
-        <v>45724</v>
-      </c>
-    </row>
-    <row r="32" spans="1:10">
-      <c r="A32">
-        <v>31</v>
-      </c>
-      <c r="B32">
-        <v>31</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>255</v>
-      </c>
-      <c r="D32" t="s">
-        <v>133</v>
-      </c>
-      <c r="E32">
-        <v>7</v>
-      </c>
-      <c r="G32">
-        <v>5</v>
-      </c>
-      <c r="H32" t="s">
-        <v>256</v>
-      </c>
-      <c r="I32" s="1">
-        <v>44556677889944</v>
-      </c>
-      <c r="J32" s="13">
-        <v>45735</v>
-      </c>
-    </row>
-    <row r="33" spans="1:10">
-      <c r="A33">
-        <v>32</v>
-      </c>
-      <c r="B33">
-        <v>32</v>
-      </c>
-      <c r="C33" s="12" t="s">
-        <v>257</v>
-      </c>
-      <c r="D33" t="s">
-        <v>137</v>
-      </c>
-      <c r="E33">
-        <v>5</v>
-      </c>
-      <c r="G33">
-        <v>2</v>
-      </c>
-      <c r="H33" t="s">
-        <v>227</v>
-      </c>
-      <c r="I33" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J33" s="13">
-        <v>45753</v>
-      </c>
-    </row>
-    <row r="34" spans="1:10">
-      <c r="A34">
-        <v>33</v>
-      </c>
-      <c r="B34">
-        <v>33</v>
-      </c>
-      <c r="C34" s="12" t="s">
-        <v>258</v>
-      </c>
-      <c r="D34" t="s">
-        <v>141</v>
-      </c>
-      <c r="E34">
-        <v>6</v>
-      </c>
-      <c r="G34">
-        <v>1</v>
-      </c>
-      <c r="H34" t="s">
-        <v>222</v>
-      </c>
-      <c r="I34" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J34" s="13">
-        <v>45764</v>
-      </c>
-    </row>
-    <row r="35" spans="1:10">
-      <c r="A35">
-        <v>34</v>
-      </c>
-      <c r="B35">
-        <v>34</v>
-      </c>
-      <c r="C35" s="12" t="s">
-        <v>245</v>
-      </c>
-      <c r="D35" t="s">
-        <v>145</v>
-      </c>
-      <c r="E35">
-        <v>2</v>
-      </c>
-      <c r="G35">
-        <v>1</v>
-      </c>
-      <c r="H35" t="s">
-        <v>222</v>
-      </c>
-      <c r="I35" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J35" s="13">
-        <v>45778</v>
-      </c>
-    </row>
-    <row r="36" spans="1:10">
-      <c r="A36">
-        <v>35</v>
-      </c>
-      <c r="B36">
-        <v>35</v>
-      </c>
-      <c r="C36" s="12" t="s">
-        <v>259</v>
-      </c>
-      <c r="D36" t="s">
-        <v>149</v>
-      </c>
-      <c r="E36">
-        <v>9</v>
-      </c>
-      <c r="G36">
-        <v>3</v>
-      </c>
-      <c r="H36" t="s">
-        <v>225</v>
-      </c>
-      <c r="I36" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J36" s="13">
-        <v>45797</v>
-      </c>
-    </row>
-    <row r="37" spans="1:10">
-      <c r="A37">
-        <v>36</v>
-      </c>
-      <c r="B37">
-        <v>36</v>
-      </c>
-      <c r="C37" s="12" t="s">
-        <v>260</v>
-      </c>
-      <c r="D37" t="s">
-        <v>152</v>
-      </c>
-      <c r="E37">
-        <v>4</v>
-      </c>
-      <c r="G37">
-        <v>2</v>
-      </c>
-      <c r="H37" t="s">
-        <v>227</v>
-      </c>
-      <c r="I37" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J37" s="13">
-        <v>45811</v>
-      </c>
-    </row>
-    <row r="38" spans="1:10">
-      <c r="A38">
-        <v>37</v>
-      </c>
-      <c r="B38">
-        <v>37</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>261</v>
-      </c>
-      <c r="D38" t="s">
-        <v>156</v>
-      </c>
-      <c r="E38">
-        <v>3</v>
-      </c>
-      <c r="G38">
-        <v>6</v>
-      </c>
-      <c r="H38" t="s">
-        <v>262</v>
-      </c>
-      <c r="I38" s="1">
-        <v>33445566778855</v>
-      </c>
-      <c r="J38" s="13">
-        <v>45835</v>
-      </c>
-    </row>
-    <row r="39" spans="1:10">
-      <c r="A39">
-        <v>38</v>
-      </c>
-      <c r="B39">
-        <v>38</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>263</v>
-      </c>
-      <c r="D39" t="s">
-        <v>160</v>
-      </c>
-      <c r="E39">
-        <v>2</v>
-      </c>
-      <c r="G39">
-        <v>1</v>
-      </c>
-      <c r="H39" t="s">
-        <v>222</v>
-      </c>
-      <c r="I39" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J39" s="13">
-        <v>45847</v>
-      </c>
-    </row>
-    <row r="40" spans="1:10">
-      <c r="A40">
-        <v>39</v>
-      </c>
-      <c r="B40">
-        <v>39</v>
-      </c>
-      <c r="C40" s="12" t="s">
-        <v>264</v>
-      </c>
-      <c r="D40" t="s">
-        <v>164</v>
-      </c>
-      <c r="E40">
-        <v>8</v>
-      </c>
-      <c r="G40">
-        <v>3</v>
-      </c>
-      <c r="H40" t="s">
-        <v>225</v>
-      </c>
-      <c r="I40" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J40" s="13">
-        <v>45863</v>
-      </c>
-    </row>
-    <row r="41" spans="1:10">
-      <c r="A41">
-        <v>40</v>
-      </c>
-      <c r="B41">
-        <v>40</v>
-      </c>
-      <c r="C41" s="12" t="s">
-        <v>265</v>
-      </c>
-      <c r="D41" t="s">
-        <v>168</v>
-      </c>
-      <c r="E41">
-        <v>6</v>
-      </c>
-      <c r="F41">
-        <v>3</v>
-      </c>
-      <c r="G41">
-        <v>2</v>
-      </c>
-      <c r="H41" t="s">
-        <v>227</v>
-      </c>
-      <c r="I41" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J41" s="13">
-        <v>45873</v>
-      </c>
-    </row>
-    <row r="42" spans="1:10">
-      <c r="A42">
-        <v>41</v>
-      </c>
-      <c r="B42">
-        <v>41</v>
-      </c>
-      <c r="C42" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="D42" t="s">
-        <v>172</v>
-      </c>
-      <c r="E42">
-        <v>1</v>
-      </c>
-      <c r="G42">
-        <v>1</v>
-      </c>
-      <c r="H42" t="s">
-        <v>222</v>
-      </c>
-      <c r="I42" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J42" s="13">
-        <v>45891</v>
-      </c>
-    </row>
-    <row r="43" spans="1:10">
-      <c r="A43">
-        <v>42</v>
-      </c>
-      <c r="B43">
-        <v>42</v>
-      </c>
-      <c r="C43" s="12" t="s">
-        <v>267</v>
-      </c>
-      <c r="D43" t="s">
-        <v>176</v>
-      </c>
-      <c r="E43">
-        <v>2</v>
-      </c>
-      <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43" t="s">
-        <v>222</v>
-      </c>
-      <c r="I43" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J43" s="13">
-        <v>45907</v>
-      </c>
-    </row>
-    <row r="44" spans="1:10">
-      <c r="A44">
-        <v>43</v>
-      </c>
-      <c r="B44">
-        <v>43</v>
-      </c>
-      <c r="C44" s="12" t="s">
-        <v>268</v>
-      </c>
-      <c r="D44" t="s">
-        <v>180</v>
-      </c>
-      <c r="E44">
-        <v>8</v>
-      </c>
-      <c r="G44">
-        <v>3</v>
-      </c>
-      <c r="H44" t="s">
-        <v>225</v>
-      </c>
-      <c r="I44" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J44" s="13">
-        <v>45918</v>
-      </c>
-    </row>
-    <row r="45" spans="1:10">
-      <c r="A45">
-        <v>44</v>
-      </c>
-      <c r="B45">
-        <v>44</v>
-      </c>
-      <c r="C45" s="12" t="s">
-        <v>269</v>
-      </c>
-      <c r="D45" t="s">
-        <v>184</v>
-      </c>
-      <c r="E45">
-        <v>9</v>
-      </c>
-      <c r="G45">
-        <v>2</v>
-      </c>
-      <c r="H45" t="s">
-        <v>227</v>
-      </c>
-      <c r="I45" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J45" s="13">
-        <v>45932</v>
-      </c>
-    </row>
-    <row r="46" spans="1:10">
-      <c r="A46">
-        <v>45</v>
-      </c>
-      <c r="B46">
-        <v>45</v>
-      </c>
-      <c r="C46" s="12" t="s">
-        <v>270</v>
-      </c>
-      <c r="D46" t="s">
-        <v>188</v>
-      </c>
-      <c r="E46">
-        <v>6</v>
-      </c>
-      <c r="G46">
-        <v>7</v>
-      </c>
-      <c r="H46" t="s">
-        <v>271</v>
-      </c>
-      <c r="I46" s="1">
-        <v>22334455667766</v>
-      </c>
-      <c r="J46" s="13">
-        <v>45951</v>
-      </c>
-    </row>
-    <row r="47" spans="1:10">
-      <c r="A47">
-        <v>46</v>
-      </c>
-      <c r="B47">
-        <v>46</v>
-      </c>
-      <c r="C47" s="12" t="s">
-        <v>272</v>
-      </c>
-      <c r="D47" t="s">
-        <v>192</v>
-      </c>
-      <c r="E47">
-        <v>2</v>
-      </c>
-      <c r="F47">
-        <v>1</v>
-      </c>
-      <c r="G47">
-        <v>1</v>
-      </c>
-      <c r="H47" t="s">
-        <v>222</v>
-      </c>
-      <c r="I47" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J47" s="13">
-        <v>45966</v>
-      </c>
-    </row>
-    <row r="48" spans="1:10">
-      <c r="A48">
-        <v>47</v>
-      </c>
-      <c r="B48">
-        <v>47</v>
-      </c>
-      <c r="C48" s="12" t="s">
-        <v>273</v>
-      </c>
-      <c r="D48" t="s">
-        <v>196</v>
-      </c>
-      <c r="E48">
-        <v>10</v>
-      </c>
-      <c r="G48">
-        <v>3</v>
-      </c>
-      <c r="H48" t="s">
-        <v>225</v>
-      </c>
-      <c r="I48" s="1">
-        <v>11223344556677</v>
-      </c>
-      <c r="J48" s="13">
-        <v>45980</v>
-      </c>
-    </row>
-    <row r="49" spans="1:10">
-      <c r="A49">
-        <v>48</v>
-      </c>
-      <c r="B49">
-        <v>48</v>
-      </c>
-      <c r="C49" s="12" t="s">
-        <v>274</v>
-      </c>
-      <c r="D49" t="s">
-        <v>200</v>
-      </c>
-      <c r="E49">
-        <v>4</v>
-      </c>
-      <c r="G49">
-        <v>2</v>
-      </c>
-      <c r="H49" t="s">
-        <v>227</v>
-      </c>
-      <c r="I49" s="1">
-        <v>98765432100022</v>
-      </c>
-      <c r="J49" s="13">
-        <v>45999</v>
-      </c>
-    </row>
-    <row r="50" spans="1:10">
-      <c r="A50">
-        <v>49</v>
-      </c>
-      <c r="B50">
-        <v>49</v>
-      </c>
-      <c r="C50" s="12" t="s">
-        <v>275</v>
-      </c>
-      <c r="D50" t="s">
-        <v>203</v>
-      </c>
-      <c r="E50">
-        <v>3</v>
-      </c>
-      <c r="G50">
-        <v>1</v>
-      </c>
-      <c r="H50" t="s">
-        <v>222</v>
-      </c>
-      <c r="I50" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J50" s="13">
-        <v>46009</v>
-      </c>
-    </row>
-    <row r="51" spans="1:10">
-      <c r="A51">
-        <v>50</v>
-      </c>
-      <c r="B51">
-        <v>50</v>
-      </c>
-      <c r="C51" s="12" t="s">
-        <v>276</v>
-      </c>
-      <c r="D51" t="s">
-        <v>207</v>
-      </c>
-      <c r="E51">
-        <v>2</v>
-      </c>
-      <c r="G51">
-        <v>1</v>
-      </c>
-      <c r="H51" t="s">
-        <v>222</v>
-      </c>
-      <c r="I51" s="1">
-        <v>12345678900011</v>
-      </c>
-      <c r="J51" s="13">
-        <v>46020</v>
-      </c>
-    </row>
-    <row r="52" spans="1:10">
-      <c r="A52">
-        <v>51</v>
-      </c>
-      <c r="B52">
-        <v>51</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>277</v>
-      </c>
-      <c r="D52" t="s">
-        <v>278</v>
-      </c>
-      <c r="E52">
-        <v>9</v>
-      </c>
-      <c r="F52">
-        <v>3</v>
-      </c>
-      <c r="G52">
-        <v>10</v>
-      </c>
-      <c r="H52" t="s">
-        <v>279</v>
-      </c>
-      <c r="I52" s="1">
-        <v>13001533200609</v>
-      </c>
-      <c r="J52" s="4">
-        <v>45291</v>
-      </c>
-    </row>
-    <row r="56" spans="1:10">
-      <c r="I56" s="15"/>
+      <c r="B10" t="s">
+        <v>413</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C246EE82-FCA8-4617-A366-829003F780A5}">
-  <dimension ref="A1:F10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="24.42578125" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:6">
-      <c r="A1" t="s">
-        <v>411</v>
-      </c>
-      <c r="B1" t="s">
-        <v>412</v>
-      </c>
-      <c r="C1" t="s">
-        <v>413</v>
-      </c>
-      <c r="D1" t="s">
-        <v>414</v>
-      </c>
-      <c r="E1" t="s">
-        <v>415</v>
-      </c>
-      <c r="F1" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>417</v>
-      </c>
-      <c r="C2" s="10" t="s">
-        <v>418</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>419</v>
-      </c>
-      <c r="C3" t="s">
-        <v>418</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>420</v>
-      </c>
-      <c r="C4" t="s">
-        <v>418</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>421</v>
-      </c>
-      <c r="C5" t="s">
-        <v>418</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-      <c r="E5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>422</v>
-      </c>
-      <c r="C6" t="s">
-        <v>423</v>
-      </c>
-      <c r="E6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>424</v>
-      </c>
-      <c r="C7" t="s">
-        <v>423</v>
-      </c>
-      <c r="E7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>425</v>
-      </c>
-      <c r="C8" t="s">
-        <v>426</v>
-      </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>427</v>
-      </c>
-      <c r="C9" t="s">
-        <v>426</v>
-      </c>
-      <c r="E9">
-        <v>1</v>
-      </c>
-      <c r="F9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>428</v>
-      </c>
-      <c r="C10" t="s">
-        <v>426</v>
-      </c>
-      <c r="F10">
-        <v>3</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB38A665-192A-4F16-A589-9DCA02DAF9D4}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="22.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>429</v>
+        <v>414</v>
       </c>
       <c r="B1" t="s">
-        <v>430</v>
+        <v>415</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
-        <v>431</v>
+        <v>7</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>416</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="B3" t="s">
-        <v>432</v>
+        <v>417</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>433</v>
+        <v>418</v>
       </c>
     </row>
   </sheetData>
@@ -7362,17 +6382,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AB4F57-4995-4803-828B-20DBAE28E207}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="B1" t="s">
-        <v>435</v>
+        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7380,7 +6403,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>436</v>
+        <v>420</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7388,7 +6411,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>437</v>
+        <v>421</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7396,7 +6419,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>438</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7404,7 +6427,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>439</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>
@@ -7412,36 +6435,36 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE98CB51-E41A-4FB9-AC1D-5CB3326537A8}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>440</v>
+        <v>424</v>
       </c>
       <c r="B1" t="s">
-        <v>441</v>
+        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>442</v>
+        <v>426</v>
       </c>
     </row>
     <row r="3" spans="1:2">
       <c r="A3">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>443</v>
+        <v>439</v>
       </c>
     </row>
   </sheetData>
@@ -7449,20 +6472,20 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B061289E-8977-40E4-BF35-B50ED0187DD6}">
   <dimension ref="A1:B10"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="17.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
       <c r="B1" t="s">
-        <v>445</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7470,7 +6493,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>446</v>
+        <v>429</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -7478,7 +6501,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>447</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -7486,7 +6509,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>448</v>
+        <v>431</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -7494,7 +6517,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>449</v>
+        <v>432</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -7502,7 +6525,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>450</v>
+        <v>433</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -7510,7 +6533,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>451</v>
+        <v>434</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -7518,7 +6541,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>452</v>
+        <v>435</v>
       </c>
     </row>
     <row r="9" spans="1:2">
@@ -7526,7 +6549,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>453</v>
+        <v>436</v>
       </c>
     </row>
     <row r="10" spans="1:2">
@@ -7534,7 +6557,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>454</v>
+        <v>437</v>
       </c>
     </row>
   </sheetData>
@@ -7545,17 +6568,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB85330-7D34-49A7-82E9-294022D99E64}">
   <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>337</v>
+        <v>332</v>
       </c>
       <c r="B1" t="s">
-        <v>444</v>
+        <v>427</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7668,9 +6691,1169 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BF6652-D73D-4218-BF00-64BC75695C73}">
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="16">
+        <v>31</v>
+      </c>
+      <c r="B2" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="16">
+        <v>33</v>
+      </c>
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="16">
+        <v>34</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="16">
+        <v>28</v>
+      </c>
+      <c r="B5" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="16">
+        <v>40</v>
+      </c>
+      <c r="B6" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="16">
+        <v>29</v>
+      </c>
+      <c r="B7" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="16">
+        <v>25</v>
+      </c>
+      <c r="B8" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="16">
+        <v>26</v>
+      </c>
+      <c r="B9" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="16">
+        <v>27</v>
+      </c>
+      <c r="B10" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="16">
+        <v>38</v>
+      </c>
+      <c r="B11" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="16">
+        <v>29</v>
+      </c>
+      <c r="B12" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="16">
+        <v>26</v>
+      </c>
+      <c r="B13" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="16">
+        <v>29</v>
+      </c>
+      <c r="B14" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="16">
+        <v>36</v>
+      </c>
+      <c r="B15" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="16">
+        <v>35</v>
+      </c>
+      <c r="B16" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="16">
+        <v>29</v>
+      </c>
+      <c r="B17" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="16">
+        <v>31</v>
+      </c>
+      <c r="B18" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="16">
+        <v>32</v>
+      </c>
+      <c r="B19" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="16">
+        <v>27</v>
+      </c>
+      <c r="B20" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="16">
+        <v>29</v>
+      </c>
+      <c r="B21" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="16">
+        <v>25</v>
+      </c>
+      <c r="B22" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="16">
+        <v>24</v>
+      </c>
+      <c r="B23" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="16">
+        <v>27</v>
+      </c>
+      <c r="B24" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="16">
+        <v>29</v>
+      </c>
+      <c r="B25" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="16">
+        <v>28</v>
+      </c>
+      <c r="B26" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="16">
+        <v>27</v>
+      </c>
+      <c r="B27" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="16">
+        <v>29</v>
+      </c>
+      <c r="B28" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="16">
+        <v>35</v>
+      </c>
+      <c r="B29" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="16">
+        <v>30</v>
+      </c>
+      <c r="B30" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="16">
+        <v>26</v>
+      </c>
+      <c r="B31" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="16">
+        <v>29</v>
+      </c>
+      <c r="B32" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="16">
+        <v>35</v>
+      </c>
+      <c r="B33" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="16">
+        <v>33</v>
+      </c>
+      <c r="B34" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="16">
+        <v>39</v>
+      </c>
+      <c r="B35" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="16">
+        <v>29</v>
+      </c>
+      <c r="B36" s="16">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280A408A-3E4C-4AFF-B78B-DB2251645EAF}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B1" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>24</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>24</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>26</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>31</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>48</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>48</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>49</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>51</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>51</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE8F9A9-A487-4868-AFA4-BF0B3BE731BD}">
+  <dimension ref="A1:I56"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="15.85546875" customWidth="1"/>
+    <col min="4" max="5" width="13.140625" customWidth="1"/>
+    <col min="7" max="7" width="14.28515625" customWidth="1"/>
+    <col min="8" max="8" width="21" customWidth="1"/>
+    <col min="9" max="9" width="22.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="12.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>440</v>
+      </c>
+      <c r="B1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C1" s="13" t="s">
+        <v>217</v>
+      </c>
+      <c r="E1" s="13"/>
+      <c r="I1"/>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="11" t="s">
+        <v>218</v>
+      </c>
+      <c r="C2" s="12">
+        <v>45297</v>
+      </c>
+      <c r="E2" s="12"/>
+      <c r="I2"/>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="11" t="s">
+        <v>220</v>
+      </c>
+      <c r="C3" s="12">
+        <v>45310</v>
+      </c>
+      <c r="E3" s="12"/>
+      <c r="I3"/>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="11" t="s">
+        <v>221</v>
+      </c>
+      <c r="C4" s="12">
+        <v>45325</v>
+      </c>
+      <c r="E4" s="12"/>
+      <c r="I4"/>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="11" t="s">
+        <v>223</v>
+      </c>
+      <c r="C5" s="12">
+        <v>45349</v>
+      </c>
+      <c r="E5" s="12"/>
+      <c r="I5"/>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="11" t="s">
+        <v>225</v>
+      </c>
+      <c r="C6" s="12">
+        <v>45362</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="I6"/>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="11" t="s">
+        <v>226</v>
+      </c>
+      <c r="C7" s="12">
+        <v>45380</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="I7"/>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>227</v>
+      </c>
+      <c r="C8" s="12">
+        <v>45389</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="I8"/>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="11" t="s">
+        <v>228</v>
+      </c>
+      <c r="C9" s="12">
+        <v>45400</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="I9"/>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="11" t="s">
+        <v>229</v>
+      </c>
+      <c r="C10" s="12">
+        <v>45414</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="I10"/>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="11" t="s">
+        <v>230</v>
+      </c>
+      <c r="C11" s="12">
+        <v>45433</v>
+      </c>
+      <c r="E11" s="12"/>
+      <c r="I11"/>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" s="11" t="s">
+        <v>231</v>
+      </c>
+      <c r="C12" s="12">
+        <v>45452</v>
+      </c>
+      <c r="E12" s="12"/>
+      <c r="I12"/>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" s="11" t="s">
+        <v>232</v>
+      </c>
+      <c r="C13" s="12">
+        <v>45468</v>
+      </c>
+      <c r="E13" s="12"/>
+      <c r="I13"/>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14">
+        <v>13</v>
+      </c>
+      <c r="B14" s="11" t="s">
+        <v>233</v>
+      </c>
+      <c r="C14" s="12">
+        <v>45477</v>
+      </c>
+      <c r="E14" s="12"/>
+      <c r="I14"/>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15">
+        <v>14</v>
+      </c>
+      <c r="B15" s="11" t="s">
+        <v>234</v>
+      </c>
+      <c r="C15" s="12">
+        <v>45492</v>
+      </c>
+      <c r="E15" s="12"/>
+      <c r="I15"/>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16" s="11" t="s">
+        <v>235</v>
+      </c>
+      <c r="C16" s="12">
+        <v>45512</v>
+      </c>
+      <c r="E16" s="12"/>
+      <c r="I16"/>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17">
+        <v>16</v>
+      </c>
+      <c r="B17" s="11" t="s">
+        <v>236</v>
+      </c>
+      <c r="C17" s="12">
+        <v>45527</v>
+      </c>
+      <c r="E17" s="12"/>
+      <c r="I17"/>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18">
+        <v>17</v>
+      </c>
+      <c r="B18" s="11" t="s">
+        <v>237</v>
+      </c>
+      <c r="C18" s="12">
+        <v>45540</v>
+      </c>
+      <c r="E18" s="12"/>
+      <c r="I18"/>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19">
+        <v>18</v>
+      </c>
+      <c r="B19" s="11" t="s">
+        <v>238</v>
+      </c>
+      <c r="C19" s="12">
+        <v>45552</v>
+      </c>
+      <c r="E19" s="12"/>
+      <c r="I19"/>
+    </row>
+    <row r="20" spans="1:9" ht="16.5" customHeight="1">
+      <c r="A20">
+        <v>19</v>
+      </c>
+      <c r="B20" s="11" t="s">
+        <v>239</v>
+      </c>
+      <c r="C20" s="12">
+        <v>45566</v>
+      </c>
+      <c r="E20" s="12"/>
+      <c r="I20"/>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21">
+        <v>20</v>
+      </c>
+      <c r="B21" s="11" t="s">
+        <v>240</v>
+      </c>
+      <c r="C21" s="12">
+        <v>45591</v>
+      </c>
+      <c r="E21" s="12"/>
+      <c r="I21"/>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22">
+        <v>21</v>
+      </c>
+      <c r="B22" s="11" t="s">
+        <v>241</v>
+      </c>
+      <c r="C22" s="12">
+        <v>45602</v>
+      </c>
+      <c r="E22" s="12"/>
+      <c r="I22"/>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23">
+        <v>22</v>
+      </c>
+      <c r="B23" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C23" s="12">
+        <v>45614</v>
+      </c>
+      <c r="E23" s="12"/>
+      <c r="I23"/>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24">
+        <v>23</v>
+      </c>
+      <c r="B24" s="11" t="s">
+        <v>243</v>
+      </c>
+      <c r="C24" s="12">
+        <v>45629</v>
+      </c>
+      <c r="E24" s="12"/>
+      <c r="I24"/>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25">
+        <v>24</v>
+      </c>
+      <c r="B25" s="11" t="s">
+        <v>244</v>
+      </c>
+      <c r="C25" s="12">
+        <v>45647</v>
+      </c>
+      <c r="E25" s="12"/>
+      <c r="I25"/>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26">
+        <v>25</v>
+      </c>
+      <c r="B26" s="11" t="s">
+        <v>245</v>
+      </c>
+      <c r="C26" s="12">
+        <v>45656</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="I26"/>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27">
+        <v>26</v>
+      </c>
+      <c r="B27" s="11" t="s">
+        <v>247</v>
+      </c>
+      <c r="C27" s="12">
+        <v>45662</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="I27"/>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28">
+        <v>27</v>
+      </c>
+      <c r="B28" s="11" t="s">
+        <v>248</v>
+      </c>
+      <c r="C28" s="12">
+        <v>45679</v>
+      </c>
+      <c r="E28" s="12"/>
+      <c r="I28"/>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29">
+        <v>28</v>
+      </c>
+      <c r="B29" s="11" t="s">
+        <v>249</v>
+      </c>
+      <c r="C29" s="12">
+        <v>45698</v>
+      </c>
+      <c r="E29" s="12"/>
+      <c r="I29"/>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30">
+        <v>29</v>
+      </c>
+      <c r="B30" s="11" t="s">
+        <v>250</v>
+      </c>
+      <c r="C30" s="12">
+        <v>45712</v>
+      </c>
+      <c r="E30" s="12"/>
+      <c r="I30"/>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31">
+        <v>30</v>
+      </c>
+      <c r="B31" s="11" t="s">
+        <v>251</v>
+      </c>
+      <c r="C31" s="12">
+        <v>45724</v>
+      </c>
+      <c r="E31" s="12"/>
+      <c r="I31"/>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32">
+        <v>31</v>
+      </c>
+      <c r="B32" s="11" t="s">
+        <v>252</v>
+      </c>
+      <c r="C32" s="12">
+        <v>45735</v>
+      </c>
+      <c r="E32" s="12"/>
+      <c r="I32"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33">
+        <v>32</v>
+      </c>
+      <c r="B33" s="11" t="s">
+        <v>254</v>
+      </c>
+      <c r="C33" s="12">
+        <v>45753</v>
+      </c>
+      <c r="E33" s="12"/>
+      <c r="I33"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34">
+        <v>33</v>
+      </c>
+      <c r="B34" s="11" t="s">
+        <v>255</v>
+      </c>
+      <c r="C34" s="12">
+        <v>45764</v>
+      </c>
+      <c r="E34" s="12"/>
+      <c r="I34"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35">
+        <v>34</v>
+      </c>
+      <c r="B35" s="11" t="s">
+        <v>242</v>
+      </c>
+      <c r="C35" s="12">
+        <v>45778</v>
+      </c>
+      <c r="E35" s="12"/>
+      <c r="I35"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36">
+        <v>35</v>
+      </c>
+      <c r="B36" s="11" t="s">
+        <v>256</v>
+      </c>
+      <c r="C36" s="12">
+        <v>45797</v>
+      </c>
+      <c r="E36" s="12"/>
+      <c r="I36"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37">
+        <v>36</v>
+      </c>
+      <c r="B37" s="11" t="s">
+        <v>257</v>
+      </c>
+      <c r="C37" s="12">
+        <v>45811</v>
+      </c>
+      <c r="E37" s="12"/>
+      <c r="I37"/>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11" t="s">
+        <v>258</v>
+      </c>
+      <c r="C38" s="12">
+        <v>45835</v>
+      </c>
+      <c r="E38" s="12"/>
+      <c r="I38"/>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39">
+        <v>38</v>
+      </c>
+      <c r="B39" s="11" t="s">
+        <v>260</v>
+      </c>
+      <c r="C39" s="12">
+        <v>45847</v>
+      </c>
+      <c r="E39" s="12"/>
+      <c r="I39"/>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40">
+        <v>39</v>
+      </c>
+      <c r="B40" s="11" t="s">
+        <v>261</v>
+      </c>
+      <c r="C40" s="12">
+        <v>45863</v>
+      </c>
+      <c r="E40" s="12"/>
+      <c r="I40"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41">
+        <v>40</v>
+      </c>
+      <c r="B41" s="11" t="s">
+        <v>262</v>
+      </c>
+      <c r="C41" s="12">
+        <v>45873</v>
+      </c>
+      <c r="E41" s="12"/>
+      <c r="I41"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42">
+        <v>41</v>
+      </c>
+      <c r="B42" s="11" t="s">
+        <v>263</v>
+      </c>
+      <c r="C42" s="12">
+        <v>45891</v>
+      </c>
+      <c r="E42" s="12"/>
+      <c r="I42"/>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43">
+        <v>42</v>
+      </c>
+      <c r="B43" s="11" t="s">
+        <v>264</v>
+      </c>
+      <c r="C43" s="12">
+        <v>45907</v>
+      </c>
+      <c r="E43" s="12"/>
+      <c r="I43"/>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44">
+        <v>43</v>
+      </c>
+      <c r="B44" s="11" t="s">
+        <v>265</v>
+      </c>
+      <c r="C44" s="12">
+        <v>45918</v>
+      </c>
+      <c r="E44" s="12"/>
+      <c r="I44"/>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11" t="s">
+        <v>266</v>
+      </c>
+      <c r="C45" s="12">
+        <v>45932</v>
+      </c>
+      <c r="E45" s="12"/>
+      <c r="I45"/>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11" t="s">
+        <v>267</v>
+      </c>
+      <c r="C46" s="12">
+        <v>45951</v>
+      </c>
+      <c r="E46" s="12"/>
+      <c r="I46"/>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47">
+        <v>46</v>
+      </c>
+      <c r="B47" s="11" t="s">
+        <v>269</v>
+      </c>
+      <c r="C47" s="12">
+        <v>45966</v>
+      </c>
+      <c r="E47" s="12"/>
+      <c r="I47"/>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48">
+        <v>47</v>
+      </c>
+      <c r="B48" s="11" t="s">
+        <v>270</v>
+      </c>
+      <c r="C48" s="12">
+        <v>45980</v>
+      </c>
+      <c r="E48" s="12"/>
+      <c r="I48"/>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49">
+        <v>48</v>
+      </c>
+      <c r="B49" s="11" t="s">
+        <v>271</v>
+      </c>
+      <c r="C49" s="12">
+        <v>45999</v>
+      </c>
+      <c r="E49" s="12"/>
+      <c r="I49"/>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="A50">
+        <v>49</v>
+      </c>
+      <c r="B50" s="11" t="s">
+        <v>272</v>
+      </c>
+      <c r="C50" s="12">
+        <v>46009</v>
+      </c>
+      <c r="E50" s="12"/>
+      <c r="I50"/>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="A51">
+        <v>50</v>
+      </c>
+      <c r="B51" s="11" t="s">
+        <v>273</v>
+      </c>
+      <c r="C51" s="12">
+        <v>46020</v>
+      </c>
+      <c r="E51" s="12"/>
+      <c r="I51"/>
+    </row>
+    <row r="52" spans="1:9" ht="30">
+      <c r="A52">
+        <v>51</v>
+      </c>
+      <c r="B52" s="11" t="s">
+        <v>274</v>
+      </c>
+      <c r="C52" s="4">
+        <v>45291</v>
+      </c>
+      <c r="E52" s="4"/>
+      <c r="I52"/>
+    </row>
+    <row r="56" spans="1:9">
+      <c r="I56" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
     <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
@@ -7683,13 +7866,13 @@
         <v>6</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="C1" t="s">
         <v>1</v>
       </c>
       <c r="D1" t="s">
-        <v>280</v>
+        <v>276</v>
       </c>
     </row>
     <row r="2" spans="1:4">
@@ -7700,10 +7883,10 @@
         <v>12345678900011</v>
       </c>
       <c r="C2" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="D2" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -7714,10 +7897,10 @@
         <v>98765432100022</v>
       </c>
       <c r="C3" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="D3" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -7728,10 +7911,10 @@
         <v>11223344556677</v>
       </c>
       <c r="C4" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="D4" t="s">
-        <v>283</v>
+        <v>279</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -7742,10 +7925,10 @@
         <v>55667788990033</v>
       </c>
       <c r="C5" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D5" t="s">
-        <v>284</v>
+        <v>280</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -7756,10 +7939,10 @@
         <v>44556677889944</v>
       </c>
       <c r="C6" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="D6" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -7770,10 +7953,10 @@
         <v>33445566778855</v>
       </c>
       <c r="C7" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>286</v>
+        <v>282</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -7784,10 +7967,10 @@
         <v>22334455667766</v>
       </c>
       <c r="C8" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="D8" t="s">
-        <v>287</v>
+        <v>283</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -7798,10 +7981,10 @@
         <v>66778899001122</v>
       </c>
       <c r="C9" t="s">
-        <v>288</v>
+        <v>284</v>
       </c>
       <c r="D9" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -7812,10 +7995,10 @@
         <v>77889900112233</v>
       </c>
       <c r="C10" t="s">
-        <v>290</v>
+        <v>286</v>
       </c>
       <c r="D10" t="s">
-        <v>291</v>
+        <v>287</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -7826,10 +8009,10 @@
         <v>13001533200609</v>
       </c>
       <c r="C11" t="s">
-        <v>279</v>
+        <v>275</v>
       </c>
       <c r="D11" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -7837,10 +8020,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF32640F-A981-44B0-85E4-2245999C081B}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29.140625" customWidth="1"/>
   </cols>
@@ -7850,7 +8033,7 @@
         <v>7</v>
       </c>
       <c r="B1" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="C1" t="s">
         <v>8</v>
@@ -7861,7 +8044,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="C2">
         <v>3</v>
@@ -7872,7 +8055,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -7883,7 +8066,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>296</v>
+        <v>292</v>
       </c>
       <c r="C4">
         <v>2</v>
@@ -7894,7 +8077,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>297</v>
+        <v>293</v>
       </c>
       <c r="C5">
         <v>1</v>
@@ -7905,7 +8088,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>298</v>
+        <v>294</v>
       </c>
       <c r="C6">
         <v>1</v>
@@ -7916,7 +8099,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>299</v>
+        <v>295</v>
       </c>
       <c r="C7">
         <v>3</v>
@@ -7926,8 +8109,8 @@
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="11" t="s">
-        <v>300</v>
+      <c r="B8" s="10" t="s">
+        <v>296</v>
       </c>
       <c r="C8">
         <v>3</v>
@@ -7938,7 +8121,7 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>301</v>
+        <v>297</v>
       </c>
       <c r="C9">
         <v>2</v>
@@ -7949,7 +8132,7 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>302</v>
+        <v>298</v>
       </c>
       <c r="C10">
         <v>3</v>
@@ -7959,8 +8142,8 @@
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="10" t="s">
-        <v>303</v>
+      <c r="B11" s="9" t="s">
+        <v>299</v>
       </c>
       <c r="C11">
         <v>3</v>
@@ -7971,10 +8154,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF866A59-0A7E-4760-9825-A3F8FA105296}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="30" customWidth="1"/>
   </cols>
@@ -7984,7 +8167,7 @@
         <v>8</v>
       </c>
       <c r="B1" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -7992,7 +8175,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8000,7 +8183,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8008,7 +8191,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
     </row>
   </sheetData>
@@ -8016,10 +8199,10 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8622C8FC-7CA6-439A-AD89-9564ADC4B774}">
   <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="29" customWidth="1"/>
   </cols>
@@ -8029,7 +8212,7 @@
         <v>9</v>
       </c>
       <c r="B1" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -8037,7 +8220,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8045,7 +8228,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8053,7 +8236,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>311</v>
+        <v>307</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -8061,7 +8244,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>312</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -8069,7 +8252,7 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>313</v>
+        <v>309</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -8077,7 +8260,7 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>314</v>
+        <v>310</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -8085,134 +8268,7 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>315</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221443EF-5CAA-4D8F-99E0-E1F7C9868982}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>318</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7368821-A8B6-4663-8B70-AAC06AB66366}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7938516-E6BC-46F7-BFB9-9A46C4854A04}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>323</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>325</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>326</v>
+        <v>311</v>
       </c>
     </row>
   </sheetData>

--- a/Tableurs Tenrac Final.xlsx
+++ b/Tableurs Tenrac Final.xlsx
@@ -1,46 +1,47 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="24332"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y25010156\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21B5BB3E-3431-4B40-B745-D9F7E12F9930}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EB0092-8FCA-45E6-9749-56050A06F1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="16" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7320" yWindow="375" windowWidth="21600" windowHeight="11295" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Tenrac" sheetId="9" r:id="rId1"/>
-    <sheet name="PARTICIPE" sheetId="28" r:id="rId2"/>
-    <sheet name="EST_COMPOSE_DE" sheetId="29" r:id="rId3"/>
-    <sheet name="EST_SUJET_A" sheetId="30" r:id="rId4"/>
-    <sheet name="Carte_membre" sheetId="12" r:id="rId5"/>
-    <sheet name="Organisme" sheetId="1" r:id="rId6"/>
-    <sheet name="Club" sheetId="2" r:id="rId7"/>
-    <sheet name="Ordre" sheetId="27" r:id="rId8"/>
-    <sheet name="Grade" sheetId="5" r:id="rId9"/>
-    <sheet name="Rang" sheetId="6" r:id="rId10"/>
-    <sheet name="Titre" sheetId="7" r:id="rId11"/>
-    <sheet name="Dignité" sheetId="8" r:id="rId12"/>
-    <sheet name="Réunion" sheetId="10" r:id="rId13"/>
-    <sheet name="Repas" sheetId="19" r:id="rId14"/>
-    <sheet name="Ingrédient" sheetId="11" r:id="rId15"/>
-    <sheet name="Légume" sheetId="20" r:id="rId16"/>
-    <sheet name="Plat" sheetId="13" r:id="rId17"/>
-    <sheet name="CONTIENT" sheetId="14" r:id="rId18"/>
-    <sheet name="machine" sheetId="17" r:id="rId19"/>
-    <sheet name="UTILISE" sheetId="21" r:id="rId20"/>
-    <sheet name="Entrerien" sheetId="18" r:id="rId21"/>
-    <sheet name="POSSEDE " sheetId="26" r:id="rId22"/>
-    <sheet name="Contrainte" sheetId="22" r:id="rId23"/>
-    <sheet name="Conviction" sheetId="25" r:id="rId24"/>
-    <sheet name="Allergene" sheetId="23" r:id="rId25"/>
-    <sheet name="Croyance" sheetId="24" r:id="rId26"/>
-    <sheet name="Sauce" sheetId="15" r:id="rId27"/>
+    <sheet name="ORGANISME" sheetId="1" r:id="rId1"/>
+    <sheet name="INGREDIENT" sheetId="11" r:id="rId2"/>
+    <sheet name="SAUCE" sheetId="15" r:id="rId3"/>
+    <sheet name="LEGUME" sheetId="20" r:id="rId4"/>
+    <sheet name="MACHINE" sheetId="17" r:id="rId5"/>
+    <sheet name="PLAT" sheetId="13" r:id="rId6"/>
+    <sheet name="COMPOSE DE" sheetId="31" r:id="rId7"/>
+    <sheet name="TITRE" sheetId="7" r:id="rId8"/>
+    <sheet name="GRADE" sheetId="5" r:id="rId9"/>
+    <sheet name="RANG" sheetId="6" r:id="rId10"/>
+    <sheet name="DIGNITE" sheetId="8" r:id="rId11"/>
+    <sheet name="CONTRAINTE" sheetId="22" r:id="rId12"/>
+    <sheet name="ORDRE" sheetId="27" r:id="rId13"/>
+    <sheet name="CONVICTION" sheetId="25" r:id="rId14"/>
+    <sheet name="CLUB" sheetId="2" r:id="rId15"/>
+    <sheet name="REUNION" sheetId="10" r:id="rId16"/>
+    <sheet name="REPAS" sheetId="19" r:id="rId17"/>
+    <sheet name="ALLERGENE" sheetId="23" r:id="rId18"/>
+    <sheet name="CROYANCE" sheetId="24" r:id="rId19"/>
+    <sheet name="TENRAC" sheetId="9" r:id="rId20"/>
+    <sheet name="CARTE" sheetId="12" r:id="rId21"/>
+    <sheet name="ENTRETIEN" sheetId="18" r:id="rId22"/>
+    <sheet name="PARTICIPE" sheetId="28" r:id="rId23"/>
+    <sheet name="EST_COMPOSE_DE" sheetId="29" r:id="rId24"/>
+    <sheet name="CONTIENT" sheetId="14" r:id="rId25"/>
+    <sheet name="UTILISE" sheetId="21" r:id="rId26"/>
+    <sheet name="POSSEDE " sheetId="26" r:id="rId27"/>
     <sheet name="ACCOMPAGNE" sheetId="16" r:id="rId28"/>
+    <sheet name="EST_SUJET_A" sheetId="30" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191028"/>
   <extLst>
@@ -64,7 +65,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="458">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="457">
   <si>
     <t>idTenrac</t>
   </si>
@@ -1308,9 +1309,6 @@
     <t xml:space="preserve">Refus de fromage trop fort  </t>
   </si>
   <si>
-    <t xml:space="preserve">idConv    </t>
-  </si>
-  <si>
     <t>nomConv</t>
   </si>
   <si>
@@ -1338,9 +1336,6 @@
     <t xml:space="preserve"> Poisson</t>
   </si>
   <si>
-    <t xml:space="preserve">idC    </t>
-  </si>
-  <si>
     <t>croyances</t>
   </si>
   <si>
@@ -1438,6 +1433,9 @@
   </si>
   <si>
     <t>lieu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">idContrainte   </t>
   </si>
 </sst>
 </file>
@@ -1551,7 +1549,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1575,6 +1573,9 @@
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1890,6 +1891,1309 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13" customWidth="1"/>
+    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="23.42578125" customWidth="1"/>
+    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1">
+        <v>12345678900011</v>
+      </c>
+      <c r="C2" t="s">
+        <v>219</v>
+      </c>
+      <c r="D2" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1">
+        <v>98765432100022</v>
+      </c>
+      <c r="C3" t="s">
+        <v>224</v>
+      </c>
+      <c r="D3" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="1">
+        <v>11223344556677</v>
+      </c>
+      <c r="C4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D4" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1">
+        <v>55667788990033</v>
+      </c>
+      <c r="C5" t="s">
+        <v>246</v>
+      </c>
+      <c r="D5" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1">
+        <v>44556677889944</v>
+      </c>
+      <c r="C6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D6" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1">
+        <v>33445566778855</v>
+      </c>
+      <c r="C7" t="s">
+        <v>259</v>
+      </c>
+      <c r="D7" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1">
+        <v>22334455667766</v>
+      </c>
+      <c r="C8" t="s">
+        <v>268</v>
+      </c>
+      <c r="D8" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1">
+        <v>66778899001122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>284</v>
+      </c>
+      <c r="D9" t="s">
+        <v>285</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1">
+        <v>77889900112233</v>
+      </c>
+      <c r="C10" t="s">
+        <v>286</v>
+      </c>
+      <c r="D10" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1">
+        <v>13001533200609</v>
+      </c>
+      <c r="C11" t="s">
+        <v>275</v>
+      </c>
+      <c r="D11" t="s">
+        <v>288</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221443EF-5CAA-4D8F-99E0-E1F7C9868982}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="11.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B1" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>314</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7938516-E6BC-46F7-BFB9-9A46C4854A04}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>12</v>
+      </c>
+      <c r="B1" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>322</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C246EE82-FCA8-4617-A366-829003F780A5}">
+  <dimension ref="A1:C10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="13.28515625" customWidth="1"/>
+    <col min="2" max="2" width="27" customWidth="1"/>
+    <col min="3" max="3" width="17.140625" customWidth="1"/>
+    <col min="4" max="4" width="12.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>403</v>
+      </c>
+      <c r="B1" t="s">
+        <v>404</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>405</v>
+      </c>
+      <c r="C2" s="9"/>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>408</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>410</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>413</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF866A59-0A7E-4760-9825-A3F8FA105296}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="30" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>302</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>303</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB38A665-192A-4F16-A589-9DCA02DAF9D4}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="25.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>456</v>
+      </c>
+      <c r="B1" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>7</v>
+      </c>
+      <c r="B2" s="9" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>8</v>
+      </c>
+      <c r="B3" t="s">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>9</v>
+      </c>
+      <c r="B4" t="s">
+        <v>417</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF32640F-A981-44B0-85E4-2245999C081B}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="29.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B1" t="s">
+        <v>289</v>
+      </c>
+      <c r="C1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>290</v>
+      </c>
+      <c r="C2">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>291</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>292</v>
+      </c>
+      <c r="C4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>293</v>
+      </c>
+      <c r="C5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>294</v>
+      </c>
+      <c r="C6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>295</v>
+      </c>
+      <c r="C7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="10" t="s">
+        <v>296</v>
+      </c>
+      <c r="C8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>297</v>
+      </c>
+      <c r="C9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>298</v>
+      </c>
+      <c r="C10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="9" t="s">
+        <v>299</v>
+      </c>
+      <c r="C11">
+        <v>3</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE11920-A5FA-41BA-B201-1543B4434A54}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="34.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C1" t="s">
+        <v>323</v>
+      </c>
+      <c r="D1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>325</v>
+      </c>
+      <c r="C2" s="3">
+        <v>46035</v>
+      </c>
+      <c r="D2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>326</v>
+      </c>
+      <c r="C3" s="3">
+        <v>46066</v>
+      </c>
+      <c r="D3">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>327</v>
+      </c>
+      <c r="C4" s="3">
+        <v>46094</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>328</v>
+      </c>
+      <c r="C5" s="3">
+        <v>46155</v>
+      </c>
+      <c r="D5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>329</v>
+      </c>
+      <c r="C6" s="3">
+        <v>46155</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>328</v>
+      </c>
+      <c r="C7" s="3">
+        <v>46216</v>
+      </c>
+      <c r="D7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>330</v>
+      </c>
+      <c r="C8" s="3">
+        <v>46278</v>
+      </c>
+      <c r="D8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>331</v>
+      </c>
+      <c r="C9" s="3">
+        <v>46308</v>
+      </c>
+      <c r="D9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>327</v>
+      </c>
+      <c r="C10" s="3">
+        <v>46339</v>
+      </c>
+      <c r="D10">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>330</v>
+      </c>
+      <c r="C11" s="3">
+        <v>46369</v>
+      </c>
+      <c r="D11">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8593E13-AF45-4F25-87C1-268A620169C2}">
+  <dimension ref="A1:C11"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="42.28515625" customWidth="1"/>
+    <col min="3" max="3" width="9.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="8" t="s">
+        <v>333</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="8" t="s">
+        <v>334</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="8" t="s">
+        <v>335</v>
+      </c>
+      <c r="C4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="8" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>337</v>
+      </c>
+      <c r="C6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="8" t="s">
+        <v>338</v>
+      </c>
+      <c r="C7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>339</v>
+      </c>
+      <c r="C8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>340</v>
+      </c>
+      <c r="C9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" s="15" t="s">
+        <v>439</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" s="8" t="s">
+        <v>341</v>
+      </c>
+      <c r="C11">
+        <v>10</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AB4F57-4995-4803-828B-20DBAE28E207}">
+  <dimension ref="A1:B5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="16.140625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>420</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>422</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE98CB51-E41A-4FB9-AC1D-5CB3326537A8}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="2" max="2" width="20.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>436</v>
+      </c>
+      <c r="B1" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>5</v>
+      </c>
+      <c r="B2" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7736852-B5A3-4EA0-90D7-EE45E8F34F53}">
+  <dimension ref="A1:B40"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="25.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>344</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>350</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>351</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11" t="s">
+        <v>353</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>12</v>
+      </c>
+      <c r="B13" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>14</v>
+      </c>
+      <c r="B14" t="s">
+        <v>356</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>15</v>
+      </c>
+      <c r="B15" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>16</v>
+      </c>
+      <c r="B16" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>17</v>
+      </c>
+      <c r="B17" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>18</v>
+      </c>
+      <c r="B18" t="s">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>19</v>
+      </c>
+      <c r="B19" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>20</v>
+      </c>
+      <c r="B20" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>21</v>
+      </c>
+      <c r="B21" t="s">
+        <v>363</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>22</v>
+      </c>
+      <c r="B22" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>23</v>
+      </c>
+      <c r="B23" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="16">
+        <v>24</v>
+      </c>
+      <c r="B24" s="16" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="16">
+        <v>25</v>
+      </c>
+      <c r="B25" s="16" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="16">
+        <v>26</v>
+      </c>
+      <c r="B26" s="16" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="16">
+        <v>27</v>
+      </c>
+      <c r="B27" s="16" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="16">
+        <v>28</v>
+      </c>
+      <c r="B28" s="16" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="16">
+        <v>29</v>
+      </c>
+      <c r="B29" s="16" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="16">
+        <v>30</v>
+      </c>
+      <c r="B30" s="16" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="16">
+        <v>31</v>
+      </c>
+      <c r="B31" s="16" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="16">
+        <v>32</v>
+      </c>
+      <c r="B32" s="16" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="16">
+        <v>33</v>
+      </c>
+      <c r="B33" s="16" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="16">
+        <v>34</v>
+      </c>
+      <c r="B34" s="16" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="16">
+        <v>35</v>
+      </c>
+      <c r="B35" s="16" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="16">
+        <v>36</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37" s="16">
+        <v>37</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38" s="16">
+        <v>38</v>
+      </c>
+      <c r="B38" s="16" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39" s="16">
+        <v>39</v>
+      </c>
+      <c r="B39" s="16" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40" s="16">
+        <v>40</v>
+      </c>
+      <c r="B40" s="16" t="s">
+        <v>445</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B1048567">
+    <sortCondition ref="B1:B1048567"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{38A6B9DE-762D-4CD8-9484-40200F975624}">
   <dimension ref="A1:M52"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -3709,3451 +5013,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{221443EF-5CAA-4D8F-99E0-E1F7C9868982}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="11.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>10</v>
-      </c>
-      <c r="B1" t="s">
-        <v>312</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>313</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>314</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7368821-A8B6-4663-8B70-AAC06AB66366}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="12.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1" t="s">
-        <v>315</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>316</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>317</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>318</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7938516-E6BC-46F7-BFB9-9A46C4854A04}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="15.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>12</v>
-      </c>
-      <c r="B1" t="s">
-        <v>319</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>320</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>321</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>322</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CDE11920-A5FA-41BA-B201-1543B4434A54}">
-  <dimension ref="A1:D11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="34.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B1" t="s">
-        <v>457</v>
-      </c>
-      <c r="C1" t="s">
-        <v>323</v>
-      </c>
-      <c r="D1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>325</v>
-      </c>
-      <c r="C2" s="3">
-        <v>46035</v>
-      </c>
-      <c r="D2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>326</v>
-      </c>
-      <c r="C3" s="3">
-        <v>46066</v>
-      </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>327</v>
-      </c>
-      <c r="C4" s="3">
-        <v>46094</v>
-      </c>
-      <c r="D4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>328</v>
-      </c>
-      <c r="C5" s="3">
-        <v>46155</v>
-      </c>
-      <c r="D5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>329</v>
-      </c>
-      <c r="C6" s="3">
-        <v>46155</v>
-      </c>
-      <c r="D6">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>328</v>
-      </c>
-      <c r="C7" s="3">
-        <v>46216</v>
-      </c>
-      <c r="D7">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>330</v>
-      </c>
-      <c r="C8" s="3">
-        <v>46278</v>
-      </c>
-      <c r="D8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>331</v>
-      </c>
-      <c r="C9" s="3">
-        <v>46308</v>
-      </c>
-      <c r="D9">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>327</v>
-      </c>
-      <c r="C10" s="3">
-        <v>46339</v>
-      </c>
-      <c r="D10">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>330</v>
-      </c>
-      <c r="C11" s="3">
-        <v>46369</v>
-      </c>
-      <c r="D11">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8593E13-AF45-4F25-87C1-268A620169C2}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="42.28515625" customWidth="1"/>
-    <col min="3" max="3" width="9.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="8" t="s">
-        <v>333</v>
-      </c>
-      <c r="C2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="8" t="s">
-        <v>334</v>
-      </c>
-      <c r="C3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="8" t="s">
-        <v>335</v>
-      </c>
-      <c r="C4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="8" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="8" t="s">
-        <v>337</v>
-      </c>
-      <c r="C6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="8" t="s">
-        <v>338</v>
-      </c>
-      <c r="C7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>339</v>
-      </c>
-      <c r="C8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>340</v>
-      </c>
-      <c r="C9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" s="15" t="s">
-        <v>441</v>
-      </c>
-      <c r="C10">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" s="8" t="s">
-        <v>341</v>
-      </c>
-      <c r="C11">
-        <v>10</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7736852-B5A3-4EA0-90D7-EE45E8F34F53}">
-  <dimension ref="A1:B40"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>342</v>
-      </c>
-      <c r="B1" t="s">
-        <v>343</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>344</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>345</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>346</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>347</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>348</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>349</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>350</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>351</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>352</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>353</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>354</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="B13" t="s">
-        <v>355</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>14</v>
-      </c>
-      <c r="B14" t="s">
-        <v>356</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>15</v>
-      </c>
-      <c r="B15" t="s">
-        <v>357</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>16</v>
-      </c>
-      <c r="B16" t="s">
-        <v>358</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>17</v>
-      </c>
-      <c r="B17" t="s">
-        <v>359</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>18</v>
-      </c>
-      <c r="B18" t="s">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>19</v>
-      </c>
-      <c r="B19" t="s">
-        <v>361</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>20</v>
-      </c>
-      <c r="B20" t="s">
-        <v>362</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>21</v>
-      </c>
-      <c r="B21" t="s">
-        <v>363</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>22</v>
-      </c>
-      <c r="B22" t="s">
-        <v>364</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23">
-        <v>23</v>
-      </c>
-      <c r="B23" t="s">
-        <v>365</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="16">
-        <v>24</v>
-      </c>
-      <c r="B24" s="16" t="s">
-        <v>448</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="16">
-        <v>25</v>
-      </c>
-      <c r="B25" s="16" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="16">
-        <v>26</v>
-      </c>
-      <c r="B26" s="16" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="16">
-        <v>27</v>
-      </c>
-      <c r="B27" s="16" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="16">
-        <v>28</v>
-      </c>
-      <c r="B28" s="16" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="16">
-        <v>29</v>
-      </c>
-      <c r="B29" s="16" t="s">
-        <v>445</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="16">
-        <v>30</v>
-      </c>
-      <c r="B30" s="16" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="16">
-        <v>31</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="16">
-        <v>32</v>
-      </c>
-      <c r="B32" s="16" t="s">
-        <v>451</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="16">
-        <v>33</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="16">
-        <v>34</v>
-      </c>
-      <c r="B34" s="16" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="16">
-        <v>35</v>
-      </c>
-      <c r="B35" s="16" t="s">
-        <v>452</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="16">
-        <v>36</v>
-      </c>
-      <c r="B36" s="16" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37" s="16">
-        <v>37</v>
-      </c>
-      <c r="B37" s="16" t="s">
-        <v>454</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38" s="16">
-        <v>38</v>
-      </c>
-      <c r="B38" s="16" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39" s="16">
-        <v>39</v>
-      </c>
-      <c r="B39" s="16" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40" s="16">
-        <v>40</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>447</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B1048567">
-    <sortCondition ref="B1:B1048567"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DDB049-21B5-47C8-B1CC-963F1F30C6BC}">
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="3" max="3" width="13.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:1">
-      <c r="A1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="2" spans="1:1">
-      <c r="A2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1">
-      <c r="A3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:1">
-      <c r="A4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:1">
-      <c r="A5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:1">
-      <c r="A6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1">
-      <c r="A7">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:1">
-      <c r="A8">
-        <v>11</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476A76D1-5D51-4DFB-BE48-DD996E1824BF}">
-  <dimension ref="A1:D12"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="34" customWidth="1"/>
-    <col min="3" max="3" width="72.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1" t="s">
-        <v>367</v>
-      </c>
-      <c r="C1" t="s">
-        <v>368</v>
-      </c>
-      <c r="D1" t="s">
-        <v>324</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>369</v>
-      </c>
-      <c r="C2" t="s">
-        <v>370</v>
-      </c>
-      <c r="D2">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>371</v>
-      </c>
-      <c r="C3" t="s">
-        <v>372</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>373</v>
-      </c>
-      <c r="C4" t="s">
-        <v>374</v>
-      </c>
-      <c r="D4">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>375</v>
-      </c>
-      <c r="C5" t="s">
-        <v>376</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>377</v>
-      </c>
-      <c r="C6" t="s">
-        <v>378</v>
-      </c>
-      <c r="D6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>379</v>
-      </c>
-      <c r="C7" t="s">
-        <v>380</v>
-      </c>
-      <c r="D7">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>381</v>
-      </c>
-      <c r="C8" t="s">
-        <v>382</v>
-      </c>
-      <c r="D8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>383</v>
-      </c>
-      <c r="C9" t="s">
-        <v>384</v>
-      </c>
-      <c r="D9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>385</v>
-      </c>
-      <c r="C10" t="s">
-        <v>386</v>
-      </c>
-      <c r="D10">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11" t="s">
-        <v>335</v>
-      </c>
-      <c r="C11" t="s">
-        <v>387</v>
-      </c>
-      <c r="D11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="B12" t="s">
-        <v>388</v>
-      </c>
-      <c r="C12" t="s">
-        <v>389</v>
-      </c>
-      <c r="D12">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A29A99-C4C2-4014-887E-65B5C0B9BBF8}">
-  <dimension ref="A1:B47"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1" t="s">
-        <v>366</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>3</v>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>4</v>
-      </c>
-      <c r="B12">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>4</v>
-      </c>
-      <c r="B13">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>5</v>
-      </c>
-      <c r="B14">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>6</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>6</v>
-      </c>
-      <c r="B17">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>6</v>
-      </c>
-      <c r="B18">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>6</v>
-      </c>
-      <c r="B19">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>7</v>
-      </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>7</v>
-      </c>
-      <c r="B21">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>7</v>
-      </c>
-      <c r="B22">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23">
-        <v>7</v>
-      </c>
-      <c r="B23">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
-        <v>7</v>
-      </c>
-      <c r="B24">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25">
-        <v>7</v>
-      </c>
-      <c r="B25">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>8</v>
-      </c>
-      <c r="B26">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
-        <v>8</v>
-      </c>
-      <c r="B27">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28">
-        <v>9</v>
-      </c>
-      <c r="B28">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
-        <v>9</v>
-      </c>
-      <c r="B29">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>9</v>
-      </c>
-      <c r="B30">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31">
-        <v>9</v>
-      </c>
-      <c r="B31">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>9</v>
-      </c>
-      <c r="B32">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>9</v>
-      </c>
-      <c r="B33">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>9</v>
-      </c>
-      <c r="B34">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>10</v>
-      </c>
-      <c r="B35">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>10</v>
-      </c>
-      <c r="B36">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>10</v>
-      </c>
-      <c r="B37">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>10</v>
-      </c>
-      <c r="B38">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>10</v>
-      </c>
-      <c r="B39">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>10</v>
-      </c>
-      <c r="B40">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>11</v>
-      </c>
-      <c r="B41">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>11</v>
-      </c>
-      <c r="B42">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>11</v>
-      </c>
-      <c r="B43">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>11</v>
-      </c>
-      <c r="B44">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>11</v>
-      </c>
-      <c r="B45">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>11</v>
-      </c>
-      <c r="B46">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>11</v>
-      </c>
-      <c r="B47">
-        <v>15</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40FC11C4-9A11-45A3-B059-AA1A3BE2A68F}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="17.7109375" customWidth="1"/>
-    <col min="3" max="3" width="16.85546875" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>390</v>
-      </c>
-      <c r="B1" t="s">
-        <v>391</v>
-      </c>
-      <c r="C1" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>393</v>
-      </c>
-      <c r="C2" t="s">
-        <v>394</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>395</v>
-      </c>
-      <c r="C3" t="s">
-        <v>396</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>397</v>
-      </c>
-      <c r="C4" t="s">
-        <v>398</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>399</v>
-      </c>
-      <c r="C5" t="s">
-        <v>400</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A125E296-0ECF-4112-ADE5-29F81271894B}">
-  <dimension ref="A1:B71"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>440</v>
-      </c>
-      <c r="B1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>10</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>10</v>
-      </c>
-      <c r="B14">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>13</v>
-      </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>15</v>
-      </c>
-      <c r="B16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>15</v>
-      </c>
-      <c r="B17">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>15</v>
-      </c>
-      <c r="B18">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>15</v>
-      </c>
-      <c r="B19">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>15</v>
-      </c>
-      <c r="B20">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>16</v>
-      </c>
-      <c r="B21">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>18</v>
-      </c>
-      <c r="B22">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23">
-        <v>18</v>
-      </c>
-      <c r="B23">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
-        <v>18</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25">
-        <v>18</v>
-      </c>
-      <c r="B25">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26">
-        <v>18</v>
-      </c>
-      <c r="B26">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27">
-        <v>19</v>
-      </c>
-      <c r="B27">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28">
-        <v>19</v>
-      </c>
-      <c r="B28">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29">
-        <v>20</v>
-      </c>
-      <c r="B29">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30">
-        <v>22</v>
-      </c>
-      <c r="B30">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31">
-        <v>22</v>
-      </c>
-      <c r="B31">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32">
-        <v>22</v>
-      </c>
-      <c r="B32">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33">
-        <v>22</v>
-      </c>
-      <c r="B33">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34">
-        <v>22</v>
-      </c>
-      <c r="B34">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35">
-        <v>23</v>
-      </c>
-      <c r="B35">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36">
-        <v>28</v>
-      </c>
-      <c r="B36">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2">
-      <c r="A37">
-        <v>28</v>
-      </c>
-      <c r="B37">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="38" spans="1:2">
-      <c r="A38">
-        <v>28</v>
-      </c>
-      <c r="B38">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="39" spans="1:2">
-      <c r="A39">
-        <v>29</v>
-      </c>
-      <c r="B39">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="40" spans="1:2">
-      <c r="A40">
-        <v>30</v>
-      </c>
-      <c r="B40">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="41" spans="1:2">
-      <c r="A41">
-        <v>31</v>
-      </c>
-      <c r="B41">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:2">
-      <c r="A42">
-        <v>31</v>
-      </c>
-      <c r="B42">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="43" spans="1:2">
-      <c r="A43">
-        <v>33</v>
-      </c>
-      <c r="B43">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="44" spans="1:2">
-      <c r="A44">
-        <v>34</v>
-      </c>
-      <c r="B44">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="45" spans="1:2">
-      <c r="A45">
-        <v>35</v>
-      </c>
-      <c r="B45">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="46" spans="1:2">
-      <c r="A46">
-        <v>37</v>
-      </c>
-      <c r="B46">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="47" spans="1:2">
-      <c r="A47">
-        <v>37</v>
-      </c>
-      <c r="B47">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="48" spans="1:2">
-      <c r="A48">
-        <v>37</v>
-      </c>
-      <c r="B48">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="49" spans="1:2">
-      <c r="A49">
-        <v>39</v>
-      </c>
-      <c r="B49">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="50" spans="1:2">
-      <c r="A50">
-        <v>39</v>
-      </c>
-      <c r="B50">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="51" spans="1:2">
-      <c r="A51">
-        <v>40</v>
-      </c>
-      <c r="B51">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="52" spans="1:2">
-      <c r="A52">
-        <v>40</v>
-      </c>
-      <c r="B52">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="53" spans="1:2">
-      <c r="A53">
-        <v>40</v>
-      </c>
-      <c r="B53">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="54" spans="1:2">
-      <c r="A54">
-        <v>40</v>
-      </c>
-      <c r="B54">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="55" spans="1:2">
-      <c r="A55">
-        <v>41</v>
-      </c>
-      <c r="B55">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="56" spans="1:2">
-      <c r="A56">
-        <v>41</v>
-      </c>
-      <c r="B56">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="57" spans="1:2">
-      <c r="A57">
-        <v>42</v>
-      </c>
-      <c r="B57">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="58" spans="1:2">
-      <c r="A58">
-        <v>43</v>
-      </c>
-      <c r="B58">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="59" spans="1:2">
-      <c r="A59">
-        <v>43</v>
-      </c>
-      <c r="B59">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:2">
-      <c r="A60">
-        <v>43</v>
-      </c>
-      <c r="B60">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="61" spans="1:2">
-      <c r="A61">
-        <v>44</v>
-      </c>
-      <c r="B61">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="62" spans="1:2">
-      <c r="A62">
-        <v>45</v>
-      </c>
-      <c r="B62">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="63" spans="1:2">
-      <c r="A63">
-        <v>45</v>
-      </c>
-      <c r="B63">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="64" spans="1:2">
-      <c r="A64">
-        <v>45</v>
-      </c>
-      <c r="B64">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="65" spans="1:2">
-      <c r="A65">
-        <v>46</v>
-      </c>
-      <c r="B65">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="66" spans="1:2">
-      <c r="A66">
-        <v>47</v>
-      </c>
-      <c r="B66">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="67" spans="1:2">
-      <c r="A67">
-        <v>47</v>
-      </c>
-      <c r="B67">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="68" spans="1:2">
-      <c r="A68">
-        <v>48</v>
-      </c>
-      <c r="B68">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="69" spans="1:2">
-      <c r="A69">
-        <v>51</v>
-      </c>
-      <c r="B69">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="70" spans="1:2">
-      <c r="A70">
-        <v>51</v>
-      </c>
-      <c r="B70">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="71" spans="1:2">
-      <c r="A71">
-        <v>51</v>
-      </c>
-      <c r="B71">
-        <v>5</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DCE8B9-25EF-4A25-8908-BEA8D48F1D2F}">
-  <dimension ref="A1:B18"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>324</v>
-      </c>
-      <c r="B1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>2</v>
-      </c>
-      <c r="B4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>3</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>3</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>4</v>
-      </c>
-      <c r="B7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>5</v>
-      </c>
-      <c r="B9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>6</v>
-      </c>
-      <c r="B10">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>6</v>
-      </c>
-      <c r="B11">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>7</v>
-      </c>
-      <c r="B12">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>8</v>
-      </c>
-      <c r="B13">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>8</v>
-      </c>
-      <c r="B14">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>9</v>
-      </c>
-      <c r="B15">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>9</v>
-      </c>
-      <c r="B16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>10</v>
-      </c>
-      <c r="B17">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>11</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35096018-BB9E-4928-A341-4382324C36A0}">
-  <dimension ref="A1:D9"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="4" max="4" width="12" style="7" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" t="s">
-        <v>401</v>
-      </c>
-      <c r="B1" s="7" t="s">
-        <v>323</v>
-      </c>
-      <c r="C1" t="s">
-        <v>440</v>
-      </c>
-      <c r="D1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" s="7">
-        <v>45425</v>
-      </c>
-      <c r="C2">
-        <v>9</v>
-      </c>
-      <c r="D2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7">
-        <v>45553</v>
-      </c>
-      <c r="C3">
-        <v>10</v>
-      </c>
-      <c r="D3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" s="7">
-        <v>45626</v>
-      </c>
-      <c r="C4">
-        <v>27</v>
-      </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" s="7">
-        <v>45718</v>
-      </c>
-      <c r="C5">
-        <v>40</v>
-      </c>
-      <c r="D5">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" s="7">
-        <v>45823</v>
-      </c>
-      <c r="C6">
-        <v>51</v>
-      </c>
-      <c r="D6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" s="7">
-        <v>45880</v>
-      </c>
-      <c r="C7">
-        <v>47</v>
-      </c>
-      <c r="D7">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" s="7">
-        <v>45948</v>
-      </c>
-      <c r="C8">
-        <v>26</v>
-      </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" s="7">
-        <v>46005</v>
-      </c>
-      <c r="C9">
-        <v>44</v>
-      </c>
-      <c r="D9">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE918DF-2E53-4F94-B75B-28FE1A378FE7}">
-  <dimension ref="A1:B24"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="14.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>402</v>
-      </c>
-      <c r="B1" t="s">
-        <v>342</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>1</v>
-      </c>
-      <c r="B3">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>1</v>
-      </c>
-      <c r="B4" s="9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>2</v>
-      </c>
-      <c r="B5">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>2</v>
-      </c>
-      <c r="B6">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>2</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>2</v>
-      </c>
-      <c r="B8">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>2</v>
-      </c>
-      <c r="B9">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>3</v>
-      </c>
-      <c r="B10">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>3</v>
-      </c>
-      <c r="B11">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>3</v>
-      </c>
-      <c r="B12">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>3</v>
-      </c>
-      <c r="B13">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>4</v>
-      </c>
-      <c r="B14">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>5</v>
-      </c>
-      <c r="B15">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>5</v>
-      </c>
-      <c r="B16">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>5</v>
-      </c>
-      <c r="B17">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>5</v>
-      </c>
-      <c r="B18">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>5</v>
-      </c>
-      <c r="B19">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20">
-        <v>7</v>
-      </c>
-      <c r="B20">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21">
-        <v>8</v>
-      </c>
-      <c r="B21">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22">
-        <v>9</v>
-      </c>
-      <c r="B22">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23">
-        <v>10</v>
-      </c>
-      <c r="B23">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24">
-        <v>10</v>
-      </c>
-      <c r="B24">
-        <v>8</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C246EE82-FCA8-4617-A366-829003F780A5}">
-  <dimension ref="A1:C10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="13.28515625" customWidth="1"/>
-    <col min="2" max="2" width="27" customWidth="1"/>
-    <col min="3" max="3" width="17.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
-        <v>403</v>
-      </c>
-      <c r="B1" t="s">
-        <v>404</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>405</v>
-      </c>
-      <c r="C2" s="9"/>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>407</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>408</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>409</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>412</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>413</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EB38A665-192A-4F16-A589-9DCA02DAF9D4}">
-  <dimension ref="A1:B4"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="22.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>414</v>
-      </c>
-      <c r="B1" t="s">
-        <v>415</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>7</v>
-      </c>
-      <c r="B2" s="9" t="s">
-        <v>416</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>9</v>
-      </c>
-      <c r="B4" t="s">
-        <v>418</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{03AB4F57-4995-4803-828B-20DBAE28E207}">
-  <dimension ref="A1:B5"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="1" max="1" width="16.140625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>438</v>
-      </c>
-      <c r="B1" t="s">
-        <v>419</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>420</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>421</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>422</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>423</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DE98CB51-E41A-4FB9-AC1D-5CB3326537A8}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="20.5703125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>424</v>
-      </c>
-      <c r="B1" t="s">
-        <v>425</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>5</v>
-      </c>
-      <c r="B2" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>6</v>
-      </c>
-      <c r="B3" t="s">
-        <v>439</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B061289E-8977-40E4-BF35-B50ED0187DD6}">
-  <dimension ref="A1:B10"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="17.42578125" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>427</v>
-      </c>
-      <c r="B1" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>429</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>431</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>437</v>
-      </c>
-    </row>
-  </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B1048576">
-    <sortCondition ref="B1:B1048576"/>
-  </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB85330-7D34-49A7-82E9-294022D99E64}">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>332</v>
-      </c>
-      <c r="B1" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="B6">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>9</v>
-      </c>
-      <c r="B11">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>9</v>
-      </c>
-      <c r="B12">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>10</v>
-      </c>
-      <c r="B13">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>11</v>
-      </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BF6652-D73D-4218-BF00-64BC75695C73}">
-  <dimension ref="A1:B36"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" s="17" t="s">
-        <v>342</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>427</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="16">
-        <v>31</v>
-      </c>
-      <c r="B2" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" s="16">
-        <v>33</v>
-      </c>
-      <c r="B3" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" s="16">
-        <v>34</v>
-      </c>
-      <c r="B4" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" s="16">
-        <v>28</v>
-      </c>
-      <c r="B5" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" s="16">
-        <v>40</v>
-      </c>
-      <c r="B6" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" s="16">
-        <v>29</v>
-      </c>
-      <c r="B7" s="16">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8" s="16">
-        <v>25</v>
-      </c>
-      <c r="B8" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9" s="16">
-        <v>26</v>
-      </c>
-      <c r="B9" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10" s="16">
-        <v>27</v>
-      </c>
-      <c r="B10" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11" s="16">
-        <v>38</v>
-      </c>
-      <c r="B11" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12" s="16">
-        <v>29</v>
-      </c>
-      <c r="B12" s="16">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13" s="16">
-        <v>26</v>
-      </c>
-      <c r="B13" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14" s="16">
-        <v>29</v>
-      </c>
-      <c r="B14" s="16">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15" s="16">
-        <v>36</v>
-      </c>
-      <c r="B15" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16" s="16">
-        <v>35</v>
-      </c>
-      <c r="B16" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17" s="16">
-        <v>29</v>
-      </c>
-      <c r="B17" s="16">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18" s="16">
-        <v>31</v>
-      </c>
-      <c r="B18" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19" s="16">
-        <v>32</v>
-      </c>
-      <c r="B19" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="20" spans="1:2">
-      <c r="A20" s="16">
-        <v>27</v>
-      </c>
-      <c r="B20" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="21" spans="1:2">
-      <c r="A21" s="16">
-        <v>29</v>
-      </c>
-      <c r="B21" s="16">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="22" spans="1:2">
-      <c r="A22" s="16">
-        <v>25</v>
-      </c>
-      <c r="B22" s="16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="23" spans="1:2">
-      <c r="A23" s="16">
-        <v>24</v>
-      </c>
-      <c r="B23" s="16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="24" spans="1:2">
-      <c r="A24" s="16">
-        <v>27</v>
-      </c>
-      <c r="B24" s="16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="25" spans="1:2">
-      <c r="A25" s="16">
-        <v>29</v>
-      </c>
-      <c r="B25" s="16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="26" spans="1:2">
-      <c r="A26" s="16">
-        <v>28</v>
-      </c>
-      <c r="B26" s="16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:2">
-      <c r="A27" s="16">
-        <v>27</v>
-      </c>
-      <c r="B27" s="16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:2">
-      <c r="A28" s="16">
-        <v>29</v>
-      </c>
-      <c r="B28" s="16">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:2">
-      <c r="A29" s="16">
-        <v>35</v>
-      </c>
-      <c r="B29" s="16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="30" spans="1:2">
-      <c r="A30" s="16">
-        <v>30</v>
-      </c>
-      <c r="B30" s="16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="31" spans="1:2">
-      <c r="A31" s="16">
-        <v>26</v>
-      </c>
-      <c r="B31" s="16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="32" spans="1:2">
-      <c r="A32" s="16">
-        <v>29</v>
-      </c>
-      <c r="B32" s="16">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="33" spans="1:2">
-      <c r="A33" s="16">
-        <v>35</v>
-      </c>
-      <c r="B33" s="16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="34" spans="1:2">
-      <c r="A34" s="16">
-        <v>33</v>
-      </c>
-      <c r="B34" s="16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:2">
-      <c r="A35" s="16">
-        <v>39</v>
-      </c>
-      <c r="B35" s="16">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:2">
-      <c r="A36" s="16">
-        <v>29</v>
-      </c>
-      <c r="B36" s="16">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280A408A-3E4C-4AFF-B78B-DB2251645EAF}">
-  <dimension ref="A1:B19"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="13.7109375" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>440</v>
-      </c>
-      <c r="B1" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3">
-        <v>5</v>
-      </c>
-      <c r="B3">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4">
-        <v>6</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5">
-        <v>6</v>
-      </c>
-      <c r="B5">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6">
-        <v>6</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7">
-        <v>7</v>
-      </c>
-      <c r="B7">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2">
-      <c r="A8">
-        <v>11</v>
-      </c>
-      <c r="B8">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2">
-      <c r="A9">
-        <v>20</v>
-      </c>
-      <c r="B9">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2">
-      <c r="A10">
-        <v>25</v>
-      </c>
-      <c r="B10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2">
-      <c r="A11">
-        <v>24</v>
-      </c>
-      <c r="B11">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2">
-      <c r="A12">
-        <v>24</v>
-      </c>
-      <c r="B12">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2">
-      <c r="A13">
-        <v>26</v>
-      </c>
-      <c r="B13">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2">
-      <c r="A14">
-        <v>31</v>
-      </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2">
-      <c r="A15">
-        <v>48</v>
-      </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2">
-      <c r="A16">
-        <v>48</v>
-      </c>
-      <c r="B16">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2">
-      <c r="A17">
-        <v>49</v>
-      </c>
-      <c r="B17">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>51</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>51</v>
-      </c>
-      <c r="B19">
-        <v>9</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CEE8F9A9-A487-4868-AFA4-BF0B3BE731BD}">
   <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
@@ -7168,7 +5028,7 @@
   <sheetData>
     <row r="1" spans="1:9">
       <c r="A1" t="s">
-        <v>440</v>
+        <v>438</v>
       </c>
       <c r="B1" t="s">
         <v>215</v>
@@ -7844,6 +5704,2271 @@
     </row>
     <row r="56" spans="1:9">
       <c r="I56" s="14"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35096018-BB9E-4928-A341-4382324C36A0}">
+  <dimension ref="A1:D9"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="4" max="4" width="12" style="7" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:4">
+      <c r="A1" t="s">
+        <v>401</v>
+      </c>
+      <c r="B1" s="7" t="s">
+        <v>323</v>
+      </c>
+      <c r="C1" t="s">
+        <v>438</v>
+      </c>
+      <c r="D1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="7">
+        <v>45425</v>
+      </c>
+      <c r="C2">
+        <v>9</v>
+      </c>
+      <c r="D2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" s="7">
+        <v>45553</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" s="7">
+        <v>45626</v>
+      </c>
+      <c r="C4">
+        <v>27</v>
+      </c>
+      <c r="D4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" s="7">
+        <v>45718</v>
+      </c>
+      <c r="C5">
+        <v>40</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" s="7">
+        <v>45823</v>
+      </c>
+      <c r="C6">
+        <v>51</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" s="7">
+        <v>45880</v>
+      </c>
+      <c r="C7">
+        <v>47</v>
+      </c>
+      <c r="D7">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" s="7">
+        <v>45948</v>
+      </c>
+      <c r="C8">
+        <v>26</v>
+      </c>
+      <c r="D8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" s="7">
+        <v>46005</v>
+      </c>
+      <c r="C9">
+        <v>44</v>
+      </c>
+      <c r="D9">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A125E296-0ECF-4112-ADE5-29F81271894B}">
+  <dimension ref="A1:B71"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B1" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>10</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>10</v>
+      </c>
+      <c r="B14">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>13</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>15</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>15</v>
+      </c>
+      <c r="B17">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>15</v>
+      </c>
+      <c r="B18">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>15</v>
+      </c>
+      <c r="B19">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>15</v>
+      </c>
+      <c r="B20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>16</v>
+      </c>
+      <c r="B21">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>18</v>
+      </c>
+      <c r="B22">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>18</v>
+      </c>
+      <c r="B23">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>18</v>
+      </c>
+      <c r="B24">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>18</v>
+      </c>
+      <c r="B25">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>18</v>
+      </c>
+      <c r="B26">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>19</v>
+      </c>
+      <c r="B27">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>19</v>
+      </c>
+      <c r="B28">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>20</v>
+      </c>
+      <c r="B29">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>22</v>
+      </c>
+      <c r="B30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>22</v>
+      </c>
+      <c r="B31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>22</v>
+      </c>
+      <c r="B32">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>22</v>
+      </c>
+      <c r="B33">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>22</v>
+      </c>
+      <c r="B34">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>23</v>
+      </c>
+      <c r="B35">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>28</v>
+      </c>
+      <c r="B36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>28</v>
+      </c>
+      <c r="B37">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>28</v>
+      </c>
+      <c r="B38">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>29</v>
+      </c>
+      <c r="B39">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>30</v>
+      </c>
+      <c r="B40">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>31</v>
+      </c>
+      <c r="B41">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>31</v>
+      </c>
+      <c r="B42">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>33</v>
+      </c>
+      <c r="B43">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>34</v>
+      </c>
+      <c r="B44">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>35</v>
+      </c>
+      <c r="B45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>37</v>
+      </c>
+      <c r="B46">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>37</v>
+      </c>
+      <c r="B47">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="48" spans="1:2">
+      <c r="A48">
+        <v>37</v>
+      </c>
+      <c r="B48">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="49" spans="1:2">
+      <c r="A49">
+        <v>39</v>
+      </c>
+      <c r="B49">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:2">
+      <c r="A50">
+        <v>39</v>
+      </c>
+      <c r="B50">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:2">
+      <c r="A51">
+        <v>40</v>
+      </c>
+      <c r="B51">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="52" spans="1:2">
+      <c r="A52">
+        <v>40</v>
+      </c>
+      <c r="B52">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="53" spans="1:2">
+      <c r="A53">
+        <v>40</v>
+      </c>
+      <c r="B53">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="54" spans="1:2">
+      <c r="A54">
+        <v>40</v>
+      </c>
+      <c r="B54">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:2">
+      <c r="A55">
+        <v>41</v>
+      </c>
+      <c r="B55">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="56" spans="1:2">
+      <c r="A56">
+        <v>41</v>
+      </c>
+      <c r="B56">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="57" spans="1:2">
+      <c r="A57">
+        <v>42</v>
+      </c>
+      <c r="B57">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:2">
+      <c r="A58">
+        <v>43</v>
+      </c>
+      <c r="B58">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="59" spans="1:2">
+      <c r="A59">
+        <v>43</v>
+      </c>
+      <c r="B59">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="60" spans="1:2">
+      <c r="A60">
+        <v>43</v>
+      </c>
+      <c r="B60">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="61" spans="1:2">
+      <c r="A61">
+        <v>44</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="62" spans="1:2">
+      <c r="A62">
+        <v>45</v>
+      </c>
+      <c r="B62">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="63" spans="1:2">
+      <c r="A63">
+        <v>45</v>
+      </c>
+      <c r="B63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:2">
+      <c r="A64">
+        <v>45</v>
+      </c>
+      <c r="B64">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="65" spans="1:2">
+      <c r="A65">
+        <v>46</v>
+      </c>
+      <c r="B65">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="66" spans="1:2">
+      <c r="A66">
+        <v>47</v>
+      </c>
+      <c r="B66">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="67" spans="1:2">
+      <c r="A67">
+        <v>47</v>
+      </c>
+      <c r="B67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:2">
+      <c r="A68">
+        <v>48</v>
+      </c>
+      <c r="B68">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="69" spans="1:2">
+      <c r="A69">
+        <v>51</v>
+      </c>
+      <c r="B69">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="70" spans="1:2">
+      <c r="A70">
+        <v>51</v>
+      </c>
+      <c r="B70">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="71" spans="1:2">
+      <c r="A71">
+        <v>51</v>
+      </c>
+      <c r="B71">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{59BF6652-D73D-4218-BF00-64BC75695C73}">
+  <dimension ref="A1:B36"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" s="17" t="s">
+        <v>342</v>
+      </c>
+      <c r="B1" s="17" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="16">
+        <v>31</v>
+      </c>
+      <c r="B2" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="16">
+        <v>33</v>
+      </c>
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="16">
+        <v>34</v>
+      </c>
+      <c r="B4" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="16">
+        <v>28</v>
+      </c>
+      <c r="B5" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="16">
+        <v>40</v>
+      </c>
+      <c r="B6" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="16">
+        <v>29</v>
+      </c>
+      <c r="B7" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="16">
+        <v>25</v>
+      </c>
+      <c r="B8" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="16">
+        <v>26</v>
+      </c>
+      <c r="B9" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="16">
+        <v>27</v>
+      </c>
+      <c r="B10" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="16">
+        <v>38</v>
+      </c>
+      <c r="B11" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="16">
+        <v>29</v>
+      </c>
+      <c r="B12" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="16">
+        <v>26</v>
+      </c>
+      <c r="B13" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14" s="16">
+        <v>29</v>
+      </c>
+      <c r="B14" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="16">
+        <v>36</v>
+      </c>
+      <c r="B15" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="16">
+        <v>35</v>
+      </c>
+      <c r="B16" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="16">
+        <v>29</v>
+      </c>
+      <c r="B17" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="16">
+        <v>31</v>
+      </c>
+      <c r="B18" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="16">
+        <v>32</v>
+      </c>
+      <c r="B19" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="16">
+        <v>27</v>
+      </c>
+      <c r="B20" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="16">
+        <v>29</v>
+      </c>
+      <c r="B21" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="16">
+        <v>25</v>
+      </c>
+      <c r="B22" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="16">
+        <v>24</v>
+      </c>
+      <c r="B23" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="16">
+        <v>27</v>
+      </c>
+      <c r="B24" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25" s="16">
+        <v>29</v>
+      </c>
+      <c r="B25" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26" s="16">
+        <v>28</v>
+      </c>
+      <c r="B26" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27" s="16">
+        <v>27</v>
+      </c>
+      <c r="B27" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28" s="16">
+        <v>29</v>
+      </c>
+      <c r="B28" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29" s="16">
+        <v>35</v>
+      </c>
+      <c r="B29" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30" s="16">
+        <v>30</v>
+      </c>
+      <c r="B30" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31" s="16">
+        <v>26</v>
+      </c>
+      <c r="B31" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32" s="16">
+        <v>29</v>
+      </c>
+      <c r="B32" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33" s="16">
+        <v>35</v>
+      </c>
+      <c r="B33" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34" s="16">
+        <v>33</v>
+      </c>
+      <c r="B34" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35" s="16">
+        <v>39</v>
+      </c>
+      <c r="B35" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36" s="16">
+        <v>29</v>
+      </c>
+      <c r="B36" s="16">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{08A29A99-C4C2-4014-887E-65B5C0B9BBF8}">
+  <dimension ref="A1:B47"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>3</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>4</v>
+      </c>
+      <c r="B12">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>4</v>
+      </c>
+      <c r="B13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>5</v>
+      </c>
+      <c r="B14">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>6</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>6</v>
+      </c>
+      <c r="B17">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>6</v>
+      </c>
+      <c r="B18">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>6</v>
+      </c>
+      <c r="B19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>7</v>
+      </c>
+      <c r="B21">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>7</v>
+      </c>
+      <c r="B22">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>7</v>
+      </c>
+      <c r="B23">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>7</v>
+      </c>
+      <c r="B24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="25" spans="1:2">
+      <c r="A25">
+        <v>7</v>
+      </c>
+      <c r="B25">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="26" spans="1:2">
+      <c r="A26">
+        <v>8</v>
+      </c>
+      <c r="B26">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="27" spans="1:2">
+      <c r="A27">
+        <v>8</v>
+      </c>
+      <c r="B27">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:2">
+      <c r="A28">
+        <v>9</v>
+      </c>
+      <c r="B28">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="29" spans="1:2">
+      <c r="A29">
+        <v>9</v>
+      </c>
+      <c r="B29">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="1:2">
+      <c r="A30">
+        <v>9</v>
+      </c>
+      <c r="B30">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:2">
+      <c r="A31">
+        <v>9</v>
+      </c>
+      <c r="B31">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="32" spans="1:2">
+      <c r="A32">
+        <v>9</v>
+      </c>
+      <c r="B32">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="33" spans="1:2">
+      <c r="A33">
+        <v>9</v>
+      </c>
+      <c r="B33">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:2">
+      <c r="A34">
+        <v>9</v>
+      </c>
+      <c r="B34">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="35" spans="1:2">
+      <c r="A35">
+        <v>10</v>
+      </c>
+      <c r="B35">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:2">
+      <c r="A36">
+        <v>10</v>
+      </c>
+      <c r="B36">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:2">
+      <c r="A37">
+        <v>10</v>
+      </c>
+      <c r="B37">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="38" spans="1:2">
+      <c r="A38">
+        <v>10</v>
+      </c>
+      <c r="B38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:2">
+      <c r="A39">
+        <v>10</v>
+      </c>
+      <c r="B39">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="40" spans="1:2">
+      <c r="A40">
+        <v>10</v>
+      </c>
+      <c r="B40">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:2">
+      <c r="A41">
+        <v>11</v>
+      </c>
+      <c r="B41">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="42" spans="1:2">
+      <c r="A42">
+        <v>11</v>
+      </c>
+      <c r="B42">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="43" spans="1:2">
+      <c r="A43">
+        <v>11</v>
+      </c>
+      <c r="B43">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="44" spans="1:2">
+      <c r="A44">
+        <v>11</v>
+      </c>
+      <c r="B44">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:2">
+      <c r="A45">
+        <v>11</v>
+      </c>
+      <c r="B45">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="46" spans="1:2">
+      <c r="A46">
+        <v>11</v>
+      </c>
+      <c r="B46">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="47" spans="1:2">
+      <c r="A47">
+        <v>11</v>
+      </c>
+      <c r="B47">
+        <v>15</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DCE8B9-25EF-4A25-8908-BEA8D48F1D2F}">
+  <dimension ref="A1:B18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>2</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>3</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>3</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>4</v>
+      </c>
+      <c r="B7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>5</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>5</v>
+      </c>
+      <c r="B9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>6</v>
+      </c>
+      <c r="B10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>6</v>
+      </c>
+      <c r="B11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>7</v>
+      </c>
+      <c r="B12">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>8</v>
+      </c>
+      <c r="B13">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>8</v>
+      </c>
+      <c r="B14">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>9</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>9</v>
+      </c>
+      <c r="B16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>10</v>
+      </c>
+      <c r="B17">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7DE918DF-2E53-4F94-B75B-28FE1A378FE7}">
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>402</v>
+      </c>
+      <c r="B1" t="s">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>1</v>
+      </c>
+      <c r="B3">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>1</v>
+      </c>
+      <c r="B4" s="9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>2</v>
+      </c>
+      <c r="B5">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>2</v>
+      </c>
+      <c r="B6">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>2</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>2</v>
+      </c>
+      <c r="B8">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>2</v>
+      </c>
+      <c r="B9">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>3</v>
+      </c>
+      <c r="B10">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>3</v>
+      </c>
+      <c r="B11">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>3</v>
+      </c>
+      <c r="B12">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>3</v>
+      </c>
+      <c r="B13">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>4</v>
+      </c>
+      <c r="B14">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>5</v>
+      </c>
+      <c r="B15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>5</v>
+      </c>
+      <c r="B16">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>5</v>
+      </c>
+      <c r="B17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>5</v>
+      </c>
+      <c r="B18">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>5</v>
+      </c>
+      <c r="B19">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20">
+        <v>7</v>
+      </c>
+      <c r="B20">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21">
+        <v>8</v>
+      </c>
+      <c r="B21">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22">
+        <v>9</v>
+      </c>
+      <c r="B22">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23">
+        <v>10</v>
+      </c>
+      <c r="B23">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24">
+        <v>10</v>
+      </c>
+      <c r="B24">
+        <v>8</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CB85330-7D34-49A7-82E9-294022D99E64}">
+  <dimension ref="A1:B14"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>332</v>
+      </c>
+      <c r="B1" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>9</v>
+      </c>
+      <c r="B11">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>9</v>
+      </c>
+      <c r="B12">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>10</v>
+      </c>
+      <c r="B13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>11</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280A408A-3E4C-4AFF-B78B-DB2251645EAF}">
+  <dimension ref="A1:B19"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="13.7109375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>438</v>
+      </c>
+      <c r="B1" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>5</v>
+      </c>
+      <c r="B3">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>6</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>6</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>6</v>
+      </c>
+      <c r="B6">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>7</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>11</v>
+      </c>
+      <c r="B8">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>20</v>
+      </c>
+      <c r="B9">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>25</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11">
+        <v>24</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12">
+        <v>24</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13">
+        <v>26</v>
+      </c>
+      <c r="B13">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="14" spans="1:2">
+      <c r="A14">
+        <v>31</v>
+      </c>
+      <c r="B14">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15">
+        <v>48</v>
+      </c>
+      <c r="B15">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16">
+        <v>48</v>
+      </c>
+      <c r="B16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17">
+        <v>49</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18">
+        <v>51</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19">
+        <v>51</v>
+      </c>
+      <c r="B19">
+        <v>9</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B061289E-8977-40E4-BF35-B50ED0187DD6}">
+  <dimension ref="A1:B10"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="17.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>425</v>
+      </c>
+      <c r="B1" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>429</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6">
+        <v>5</v>
+      </c>
+      <c r="B6" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8">
+        <v>7</v>
+      </c>
+      <c r="B8" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9">
+        <v>8</v>
+      </c>
+      <c r="B9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10">
+        <v>9</v>
+      </c>
+      <c r="B10" t="s">
+        <v>435</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="B1:B1048576">
+    <sortCondition ref="B1:B1048576"/>
+  </sortState>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{73DDB049-21B5-47C8-B1CC-963F1F30C6BC}">
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="3" max="3" width="13.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1">
+      <c r="A1" t="s">
+        <v>366</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1">
+      <c r="A2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1">
+      <c r="A3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1">
+      <c r="A4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1">
+      <c r="A5">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1">
+      <c r="A6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1">
+      <c r="A7">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1">
+      <c r="A8">
+        <v>11</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{40FC11C4-9A11-45A3-B059-AA1A3BE2A68F}">
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
+  <cols>
+    <col min="2" max="2" width="17.7109375" customWidth="1"/>
+    <col min="3" max="3" width="16.85546875" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" t="s">
+        <v>390</v>
+      </c>
+      <c r="B1" t="s">
+        <v>391</v>
+      </c>
+      <c r="C1" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
+        <v>393</v>
+      </c>
+      <c r="C2" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3">
+        <v>2</v>
+      </c>
+      <c r="B3" t="s">
+        <v>395</v>
+      </c>
+      <c r="C3" t="s">
+        <v>396</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3">
+      <c r="A4">
+        <v>3</v>
+      </c>
+      <c r="B4" t="s">
+        <v>397</v>
+      </c>
+      <c r="C4" t="s">
+        <v>398</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="A5">
+        <v>4</v>
+      </c>
+      <c r="B5" t="s">
+        <v>399</v>
+      </c>
+      <c r="C5" t="s">
+        <v>400</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7851,168 +7976,180 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{476A76D1-5D51-4DFB-BE48-DD996E1824BF}">
+  <dimension ref="A1:D12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="20.7109375" style="1" customWidth="1"/>
-    <col min="3" max="3" width="23.42578125" customWidth="1"/>
-    <col min="4" max="4" width="25.28515625" customWidth="1"/>
+    <col min="2" max="2" width="34" customWidth="1"/>
+    <col min="3" max="3" width="72.140625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
       <c r="A1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>216</v>
+        <v>332</v>
+      </c>
+      <c r="B1" t="s">
+        <v>367</v>
       </c>
       <c r="C1" t="s">
-        <v>1</v>
+        <v>368</v>
       </c>
       <c r="D1" t="s">
-        <v>276</v>
+        <v>324</v>
       </c>
     </row>
     <row r="2" spans="1:4">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="B2" s="1">
-        <v>12345678900011</v>
+      <c r="B2" t="s">
+        <v>369</v>
       </c>
       <c r="C2" t="s">
-        <v>219</v>
-      </c>
-      <c r="D2" t="s">
-        <v>277</v>
+        <v>370</v>
+      </c>
+      <c r="D2">
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="B3" s="1">
-        <v>98765432100022</v>
+      <c r="B3" t="s">
+        <v>371</v>
       </c>
       <c r="C3" t="s">
-        <v>224</v>
-      </c>
-      <c r="D3" t="s">
-        <v>278</v>
+        <v>372</v>
+      </c>
+      <c r="D3">
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="B4" s="1">
-        <v>11223344556677</v>
+      <c r="B4" t="s">
+        <v>373</v>
       </c>
       <c r="C4" t="s">
-        <v>222</v>
-      </c>
-      <c r="D4" t="s">
-        <v>279</v>
+        <v>374</v>
+      </c>
+      <c r="D4">
+        <v>10</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="B5" s="1">
-        <v>55667788990033</v>
+      <c r="B5" t="s">
+        <v>375</v>
       </c>
       <c r="C5" t="s">
-        <v>246</v>
-      </c>
-      <c r="D5" t="s">
-        <v>280</v>
+        <v>376</v>
+      </c>
+      <c r="D5">
+        <v>4</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6">
         <v>5</v>
       </c>
-      <c r="B6" s="1">
-        <v>44556677889944</v>
+      <c r="B6" t="s">
+        <v>377</v>
       </c>
       <c r="C6" t="s">
-        <v>253</v>
-      </c>
-      <c r="D6" t="s">
-        <v>281</v>
+        <v>378</v>
+      </c>
+      <c r="D6">
+        <v>9</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7">
         <v>6</v>
       </c>
-      <c r="B7" s="1">
-        <v>33445566778855</v>
+      <c r="B7" t="s">
+        <v>379</v>
       </c>
       <c r="C7" t="s">
-        <v>259</v>
-      </c>
-      <c r="D7" t="s">
-        <v>282</v>
+        <v>380</v>
+      </c>
+      <c r="D7">
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8">
         <v>7</v>
       </c>
-      <c r="B8" s="1">
-        <v>22334455667766</v>
+      <c r="B8" t="s">
+        <v>381</v>
       </c>
       <c r="C8" t="s">
-        <v>268</v>
-      </c>
-      <c r="D8" t="s">
-        <v>283</v>
+        <v>382</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9">
         <v>8</v>
       </c>
-      <c r="B9" s="1">
-        <v>66778899001122</v>
+      <c r="B9" t="s">
+        <v>383</v>
       </c>
       <c r="C9" t="s">
-        <v>284</v>
-      </c>
-      <c r="D9" t="s">
-        <v>285</v>
+        <v>384</v>
+      </c>
+      <c r="D9">
+        <v>8</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10">
         <v>9</v>
       </c>
-      <c r="B10" s="1">
-        <v>77889900112233</v>
+      <c r="B10" t="s">
+        <v>385</v>
       </c>
       <c r="C10" t="s">
-        <v>286</v>
-      </c>
-      <c r="D10" t="s">
-        <v>287</v>
+        <v>386</v>
+      </c>
+      <c r="D10">
+        <v>6</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11">
         <v>10</v>
       </c>
-      <c r="B11" s="1">
-        <v>13001533200609</v>
+      <c r="B11" t="s">
+        <v>335</v>
       </c>
       <c r="C11" t="s">
-        <v>275</v>
-      </c>
-      <c r="D11" t="s">
-        <v>288</v>
+        <v>387</v>
+      </c>
+      <c r="D11">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4">
+      <c r="A12">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>388</v>
+      </c>
+      <c r="C12" t="s">
+        <v>389</v>
+      </c>
+      <c r="D12">
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -8021,153 +8158,222 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FF32640F-A981-44B0-85E4-2245999C081B}">
-  <dimension ref="A1:C11"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="2" width="29.140625" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EDE184EB-6990-4149-9EDD-D56554FF9A85}">
+  <dimension ref="A1:B24"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:2">
+      <c r="A1" s="18" t="s">
+        <v>324</v>
+      </c>
+      <c r="B1" s="18" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="16">
+        <v>1</v>
+      </c>
+      <c r="B2" s="16">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
-        <v>289</v>
-      </c>
-      <c r="C1" t="s">
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" s="16">
+        <v>1</v>
+      </c>
+      <c r="B3" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" s="16">
+        <v>1</v>
+      </c>
+      <c r="B4" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" s="16">
+        <v>2</v>
+      </c>
+      <c r="B5" s="16">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" s="16">
+        <v>2</v>
+      </c>
+      <c r="B6" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" s="16">
+        <v>3</v>
+      </c>
+      <c r="B7" s="16">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" s="16">
+        <v>3</v>
+      </c>
+      <c r="B8" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" s="16">
+        <v>4</v>
+      </c>
+      <c r="B9" s="16">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" s="16">
+        <v>4</v>
+      </c>
+      <c r="B10" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" s="16">
+        <v>5</v>
+      </c>
+      <c r="B11" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2">
+      <c r="A12" s="16">
+        <v>5</v>
+      </c>
+      <c r="B12" s="16">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2">
+      <c r="A13" s="16">
+        <v>5</v>
+      </c>
+      <c r="B13" s="16">
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
-        <v>290</v>
-      </c>
-      <c r="C2">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3">
-      <c r="A3">
-        <v>2</v>
-      </c>
-      <c r="B3" t="s">
-        <v>291</v>
-      </c>
-      <c r="C3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3">
-      <c r="A4">
-        <v>3</v>
-      </c>
-      <c r="B4" t="s">
-        <v>292</v>
-      </c>
-      <c r="C4">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3">
-      <c r="A5">
-        <v>4</v>
-      </c>
-      <c r="B5" t="s">
-        <v>293</v>
-      </c>
-      <c r="C5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3">
-      <c r="A6">
+    <row r="14" spans="1:2">
+      <c r="A14" s="16">
+        <v>6</v>
+      </c>
+      <c r="B14" s="16">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:2">
+      <c r="A15" s="16">
+        <v>6</v>
+      </c>
+      <c r="B15" s="16">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:2">
+      <c r="A16" s="16">
+        <v>7</v>
+      </c>
+      <c r="B16" s="16">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:2">
+      <c r="A17" s="16">
+        <v>7</v>
+      </c>
+      <c r="B17" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:2">
+      <c r="A18" s="16">
+        <v>8</v>
+      </c>
+      <c r="B18" s="16">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="19" spans="1:2">
+      <c r="A19" s="16">
+        <v>8</v>
+      </c>
+      <c r="B19" s="16">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:2">
+      <c r="A20" s="16">
+        <v>9</v>
+      </c>
+      <c r="B20" s="16">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" spans="1:2">
+      <c r="A21" s="16">
+        <v>9</v>
+      </c>
+      <c r="B21" s="16">
         <v>5</v>
       </c>
-      <c r="B6" t="s">
-        <v>294</v>
-      </c>
-      <c r="C6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:3">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="B7" t="s">
-        <v>295</v>
-      </c>
-      <c r="C7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:3">
-      <c r="A8">
+    </row>
+    <row r="22" spans="1:2">
+      <c r="A22" s="16">
+        <v>10</v>
+      </c>
+      <c r="B22" s="16">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:2">
+      <c r="A23" s="16">
+        <v>10</v>
+      </c>
+      <c r="B23" s="16">
         <v>7</v>
       </c>
-      <c r="B8" s="10" t="s">
-        <v>296</v>
-      </c>
-      <c r="C8">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="9" spans="1:3">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="B9" t="s">
-        <v>297</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10" spans="1:3">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="B10" t="s">
-        <v>298</v>
-      </c>
-      <c r="C10">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="11" spans="1:3">
-      <c r="A11">
+    </row>
+    <row r="24" spans="1:2">
+      <c r="A24" s="16">
         <v>10</v>
       </c>
-      <c r="B11" s="9" t="s">
-        <v>299</v>
-      </c>
-      <c r="C11">
-        <v>3</v>
+      <c r="B24" s="16">
+        <v>11</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF866A59-0A7E-4760-9825-A3F8FA105296}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7368821-A8B6-4663-8B70-AAC06AB66366}">
   <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="2" max="2" width="30" customWidth="1"/>
+    <col min="2" max="2" width="12.85546875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="B1" t="s">
-        <v>300</v>
+        <v>315</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -8175,7 +8381,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>301</v>
+        <v>316</v>
       </c>
     </row>
     <row r="3" spans="1:2">
@@ -8183,7 +8389,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>302</v>
+        <v>317</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -8191,7 +8397,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>303</v>
+        <v>318</v>
       </c>
     </row>
   </sheetData>

--- a/Tableurs Tenrac Final.xlsx
+++ b/Tableurs Tenrac Final.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\y25010156\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10EB0092-8FCA-45E6-9749-56050A06F1DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D355339-B538-4744-88F3-AC694BC97FEE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7320" yWindow="375" windowWidth="21600" windowHeight="11295" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="19" activeTab="28" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ORGANISME" sheetId="1" r:id="rId1"/>
@@ -1446,7 +1446,7 @@
     <numFmt numFmtId="164" formatCode="0#&quot; &quot;##&quot; &quot;##&quot; &quot;##&quot; &quot;##"/>
     <numFmt numFmtId="165" formatCode="dd/mm/yy;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1506,6 +1506,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -1549,7 +1557,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1574,8 +1582,24 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1902,16 +1926,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="21" t="s">
         <v>216</v>
       </c>
-      <c r="C1" t="s">
-        <v>1</v>
-      </c>
-      <c r="D1" t="s">
+      <c r="C1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="20" t="s">
         <v>276</v>
       </c>
     </row>
@@ -2069,10 +2093,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>312</v>
       </c>
     </row>
@@ -2106,10 +2130,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>12</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>319</v>
       </c>
     </row>
@@ -2154,10 +2178,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>403</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>404</v>
       </c>
     </row>
@@ -2248,10 +2272,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>300</v>
       </c>
     </row>
@@ -2294,10 +2318,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>456</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>414</v>
       </c>
     </row>
@@ -2339,13 +2363,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>289</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="20" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2473,16 +2497,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>455</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="20" t="s">
         <v>323</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="20" t="s">
         <v>7</v>
       </c>
     </row>
@@ -2641,13 +2665,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
+      <c r="B1" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -2747,7 +2771,7 @@
         <v>439</v>
       </c>
       <c r="C10">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="11" spans="1:3">
@@ -2772,13 +2796,14 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.140625" customWidth="1"/>
+    <col min="2" max="2" width="12.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>418</v>
       </c>
     </row>
@@ -2824,15 +2849,15 @@
   <dimension ref="A1:B3"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="12.28515625" customWidth="1"/>
+    <col min="1" max="1" width="13.7109375" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>436</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>423</v>
       </c>
     </row>
@@ -2866,10 +2891,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>342</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>343</v>
       </c>
     </row>
@@ -3202,47 +3227,48 @@
     <col min="4" max="4" width="31.28515625" customWidth="1"/>
     <col min="5" max="5" width="15.28515625" style="2" customWidth="1"/>
     <col min="6" max="6" width="39.85546875" customWidth="1"/>
+    <col min="7" max="7" width="18.42578125" customWidth="1"/>
     <col min="8" max="8" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:13">
-      <c r="A1" t="s">
+      <c r="A1" s="18" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="2" t="s">
+      <c r="B1" s="18" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="18" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="18" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="19" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="18" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="G1" s="18" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="18" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="18" t="s">
         <v>12</v>
       </c>
     </row>
@@ -5018,6 +5044,7 @@
   <dimension ref="A1:I56"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <cols>
+    <col min="2" max="2" width="19.140625" customWidth="1"/>
     <col min="3" max="3" width="15.85546875" customWidth="1"/>
     <col min="4" max="5" width="13.140625" customWidth="1"/>
     <col min="7" max="7" width="14.28515625" customWidth="1"/>
@@ -5027,13 +5054,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>215</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="23" t="s">
         <v>217</v>
       </c>
       <c r="E1" s="13"/>
@@ -5719,16 +5746,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>401</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="24" t="s">
         <v>323</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="20" t="s">
         <v>390</v>
       </c>
     </row>
@@ -5855,10 +5882,10 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>13</v>
       </c>
     </row>
@@ -6731,10 +6758,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>366</v>
       </c>
     </row>
@@ -7113,14 +7140,14 @@
 
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{46DCE8B9-25EF-4A25-8908-BEA8D48F1D2F}">
-  <dimension ref="A1:B18"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>324</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>390</v>
       </c>
     </row>
@@ -7244,7 +7271,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:2">
+    <row r="17" spans="1:7">
       <c r="A17">
         <v>10</v>
       </c>
@@ -7252,13 +7279,16 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:2">
+    <row r="18" spans="1:7">
       <c r="A18">
         <v>11</v>
       </c>
       <c r="B18">
         <v>2</v>
       </c>
+    </row>
+    <row r="31" spans="1:7">
+      <c r="G31" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7274,10 +7304,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>402</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>342</v>
       </c>
     </row>
@@ -7476,10 +7506,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>425</v>
       </c>
     </row>
@@ -7594,17 +7624,17 @@
 
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{280A408A-3E4C-4AFF-B78B-DB2251645EAF}">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="2" max="2" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>438</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>436</v>
       </c>
     </row>
@@ -7734,22 +7764,6 @@
       </c>
       <c r="B17">
         <v>1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2">
-      <c r="A18">
-        <v>51</v>
-      </c>
-      <c r="B18">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="19" spans="1:2">
-      <c r="A19">
-        <v>51</v>
-      </c>
-      <c r="B19">
-        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -7766,10 +7780,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>425</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>426</v>
       </c>
     </row>
@@ -7862,7 +7876,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:1">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>366</v>
       </c>
     </row>
@@ -7916,24 +7930,24 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>390</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>391</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="20" t="s">
         <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:3">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="22">
+        <v>1</v>
+      </c>
+      <c r="B2" s="22" t="s">
         <v>393</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="22" t="s">
         <v>394</v>
       </c>
     </row>
@@ -7985,16 +7999,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>332</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>367</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="20" t="s">
         <v>368</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="20" t="s">
         <v>324</v>
       </c>
     </row>
@@ -8163,10 +8177,10 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="17" t="s">
         <v>324</v>
       </c>
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="17" t="s">
         <v>332</v>
       </c>
     </row>
@@ -8369,10 +8383,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="18" t="s">
         <v>315</v>
       </c>
     </row>
@@ -8414,10 +8428,10 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
-      <c r="A1" t="s">
+      <c r="A1" s="20" t="s">
         <v>9</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="20" t="s">
         <v>304</v>
       </c>
     </row>
